--- a/data/xlsx/pesel.xlsx
+++ b/data/xlsx/pesel.xlsx
@@ -200,7 +200,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>anna.kowalska@astra-finance.pl</t>
+          <t>anna.kowalska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -287,7 +287,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>t.nowacki@biuro.pl</t>
+          <t>t.nowacki@onet.pl</t>
         </is>
       </c>
     </row>
@@ -374,7 +374,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>wisniewska.katarzyna@poczta.pl</t>
+          <t>wisniewska.katarzyna@brak-domeny</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>krzysztofwojcik@mail.pl</t>
+          <t>krzysztofwojcik@o2.pl</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ewa_kowalczyk@nova-data.pl</t>
+          <t>ewa_kowalczyk@proton.me</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>adam.kaminski95@wp.pl</t>
+          <t>adam.kaminski95@outlook.com</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>monika.lewandowska@gmail.com</t>
+          <t>monika.lewandowska@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>m.zielinski@proton.me</t>
+          <t>m.zielinski@localhost</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>szymanska.barbara@silesia-invest.pl</t>
+          <t>szymanska.barbara@gmail.com</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>rafaldabrowski@poczta.pl</t>
+          <t>rafaldabrowski@wp.pl</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>anna_mazur@mail.pl</t>
+          <t>anna_mazur@onet.pl</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>tomasz.krawczyk72@onet.pl</t>
+          <t>tomasz.krawczyk72@interia.pl</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>katarzyna.wozniak@helios-markets.pl</t>
+          <t>katarzyna.wozniak@brak-domeny</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>k.jankowski@gmail.com</t>
+          <t>k.jankowski@proton.me</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>grabowska.ewa@proton.me</t>
+          <t>grabowska.ewa@outlook.com</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>adampawlak@biuro.pl</t>
+          <t>adampawlak@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>monika_michalska@polaris-capital.pl</t>
+          <t>monika_michalska@icloud.com</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>marek.krol78@mail.pl</t>
+          <t>marek.krol78@localhost</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>barbara.wieczorek@onet.pl</t>
+          <t>barbara.wieczorek@wp.pl</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>r.jablonski@wp.pl</t>
+          <t>r.jablonski@onet.pl</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>witkowska.anna@astra-finance.pl</t>
+          <t>witkowska.anna@interia.pl</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>tomaszwalczak@proton.me</t>
+          <t>tomaszwalczak@o2.pl</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>katarzyna_stepien@biuro.pl</t>
+          <t>katarzyna_stepien@brak-domeny</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>krzysztof.baran84@poczta.pl</t>
+          <t>krzysztof.baran84@outlook.com</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ewa.rutkowska@nova-data.pl</t>
+          <t>ewa.rutkowska@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>a.gorski@onet.pl</t>
+          <t>a.gorski@icloud.com</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>sikora.monika@wp.pl</t>
+          <t>sikora.monika@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>barbara_tomaszewska@silesia-invest.pl</t>
+          <t>barbara_tomaszewska@localhost</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>rafal.zajac90@biuro.pl</t>
+          <t>rafal.zajac90@onet.pl</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>anna.pietrzak@poczta.pl</t>
+          <t>anna.pietrzak@interia.pl</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>t.wojcicki@mail.pl</t>
+          <t>t.wojcicki@o2.pl</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>czarnecka.katarzyna@helios-markets.pl</t>
+          <t>czarnecka.katarzyna@proton.me</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>krzysztoflis@wp.pl</t>
+          <t>krzysztoflis@brak-domeny</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>ewa_kolodziej@gmail.com</t>
+          <t>ewa_kolodziej@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>adam.kaczmarek96@proton.me</t>
+          <t>adam.kaczmarek96@icloud.com</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>monika.piatek@polaris-capital.pl</t>
+          <t>monika.piatek@gmail.com</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>m.sadowski@poczta.pl</t>
+          <t>m.sadowski@wp.pl</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>wlodarczyk.barbara@mail.pl</t>
+          <t>wlodarczyk.barbara@localhost</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>rafalborkowski@onet.pl</t>
+          <t>rafalborkowski@interia.pl</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>anna_kowalska@astra-finance.pl</t>
+          <t>anna_kowalska@o2.pl</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>tomasz.nowacki73@gmail.com</t>
+          <t>tomasz.nowacki73@proton.me</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>katarzyna.wisniewska@proton.me</t>
+          <t>katarzyna.wisniewska@outlook.com</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>k.wojcik@biuro.pl</t>
+          <t>k.wojcik@brak-domeny</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>kowalczyk.ewa@nova-data.pl</t>
+          <t>kowalczyk.ewa@icloud.com</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>adamkaminski@mail.pl</t>
+          <t>adamkaminski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>monika_lewandowska@onet.pl</t>
+          <t>monika_lewandowska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>marek.zielinski79@wp.pl</t>
+          <t>marek.zielinski79@onet.pl</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>barbara.szymanska@silesia-invest.pl</t>
+          <t>barbara.szymanska@localhost</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>r.dabrowski@proton.me</t>
+          <t>r.dabrowski@o2.pl</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>mazur.anna@biuro.pl</t>
+          <t>mazur.anna@proton.me</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>tomaszkrawczyk@poczta.pl</t>
+          <t>tomaszkrawczyk@outlook.com</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>katarzyna_wozniak@helios-markets.pl</t>
+          <t>katarzyna_wozniak@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>krzysztof.jankowski85@onet.pl</t>
+          <t>krzysztof.jankowski85@icloud.com</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ewa.grabowska@wp.pl</t>
+          <t>ewa.grabowska@gmail.com</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>a.pawlak@gmail.com</t>
+          <t>a.pawlak@wp.pl</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>michalska.monika@polaris-capital.pl</t>
+          <t>michalska.monika@onet.pl</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>marekkrol@biuro.pl</t>
+          <t>marekkrol@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>barbara_wieczorek@poczta.pl</t>
+          <t>barbara_wieczorek@o2.pl</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>rafal.jablonski91@mail.pl</t>
+          <t>rafal.jablonski91@proton.me</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>anna.witkowska@astra-finance.pl</t>
+          <t>anna.witkowska@outlook.com</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>t.walczak@wp.pl</t>
+          <t>t.walczak@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>stepien.katarzyna@gmail.com</t>
+          <t>stepien.katarzyna@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>krzysztofbaran@proton.me</t>
+          <t>krzysztofbaran@gmail.com</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ewa_rutkowska@nova-data.pl</t>
+          <t>ewa_rutkowska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>adam.gorski97@poczta.pl</t>
+          <t>adam.gorski97@onet.pl</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>monika.sikora@mail.pl</t>
+          <t>monika.sikora@interia.pl</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>m.ostrowski@onet.pl</t>
+          <t>m.ostrowski@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>tomaszewska.barbara@silesia-invest.pl</t>
+          <t>tomaszewska.barbara@proton.me</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>rafalzajac@gmail.com</t>
+          <t>rafalzajac@outlook.com</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>anna_pietrzak@proton.me</t>
+          <t>anna_pietrzak@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>tomasz.wojcicki74@biuro.pl</t>
+          <t>tomasz.wojcicki74@icloud.com</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>katarzyna.czarnecka@helios-markets.pl</t>
+          <t>katarzyna.czarnecka@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>k.lis@mail.pl</t>
+          <t>k.lis@wp.pl</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>adamkaczmarek@wp.pl</t>
+          <t>adamkaczmarek@interia.pl</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>monika_piatek@polaris-capital.pl</t>
+          <t>monika_piatek@o2.pl</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>marek.sadowski80@proton.me</t>
+          <t>marek.sadowski80@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>barbara.wlodarczyk@biuro.pl</t>
+          <t>barbara.wlodarczyk@outlook.com</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>r.borkowski@poczta.pl</t>
+          <t>r.borkowski@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>kowalska.anna@astra-finance.pl</t>
+          <t>kowalska.anna@icloud.com</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>tomasznowacki@onet.pl</t>
+          <t>tomasznowacki@gmail.com</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>katarzyna_wisniewska@wp.pl</t>
+          <t>katarzyna_wisniewska@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>krzysztof.wojcik86@gmail.com</t>
+          <t>krzysztof.wojcik86@onet.pl</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ewa.kowalczyk@nova-data.pl</t>
+          <t>ewa.kowalczyk@interia.pl</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>a.kaminski@biuro.pl</t>
+          <t>a.kaminski@o2.pl</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>lewandowska.monika@poczta.pl</t>
+          <t>lewandowska.monika@proton.me</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>marekzielinski@mail.pl</t>
+          <t>marekzielinski@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>barbara_szymanska@silesia-invest.pl</t>
+          <t>barbara_szymanska@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>rafal.dabrowski92@wp.pl</t>
+          <t>rafal.dabrowski92@icloud.com</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>t.krawczyk@proton.me</t>
+          <t>t.krawczyk@wp.pl</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>wozniak.katarzyna@helios-markets.pl</t>
+          <t>wozniak.katarzyna@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>krzysztofjankowski@poczta.pl</t>
+          <t>krzysztofjankowski@interia.pl</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ewa_grabowska@mail.pl</t>
+          <t>ewa_grabowska@o2.pl</t>
         </is>
       </c>
     </row>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>adam.pawlak98@onet.pl</t>
+          <t>adam.pawlak98@proton.me</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>monika.michalska@polaris-capital.pl</t>
+          <t>monika.michalska@outlook.com</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>m.krol@gmail.com</t>
+          <t>m.krol@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>wieczorek.barbara@proton.me</t>
+          <t>wieczorek.barbara@icloud.com</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>rafaljablonski@biuro.pl</t>
+          <t>rafaljablonski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>anna_witkowska@astra-finance.pl</t>
+          <t>anna_witkowska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>tomasz.walczak75@mail.pl</t>
+          <t>tomasz.walczak75@onet.pl</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>katarzyna.stepien@onet.pl</t>
+          <t>katarzyna.stepien@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>k.baran@wp.pl</t>
+          <t>k.baran@o2.pl</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>rutkowska.ewa@nova-data.pl</t>
+          <t>rutkowska.ewa@proton.me</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>adamgorski@proton.me</t>
+          <t>adamgorski@outlook.com</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>monika_sikora@biuro.pl</t>
+          <t>monika_sikora@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>marek.ostrowski81@poczta.pl</t>
+          <t>marek.ostrowski81@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>barbara.tomaszewska@silesia-invest.pl</t>
+          <t>barbara.tomaszewska@gmail.com</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>r.zajac@onet.pl</t>
+          <t>r.zajac@wp.pl</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>pietrzak.anna@wp.pl</t>
+          <t>pietrzak.anna@onet.pl</t>
         </is>
       </c>
     </row>
@@ -9857,7 +9857,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>tomaszwojcicki@gmail.com</t>
+          <t>tomaszwojcicki@interia.pl</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>katarzyna_czarnecka@helios-markets.pl</t>
+          <t>katarzyna_czarnecka@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>krzysztof.lis87@biuro.pl</t>
+          <t>krzysztof.lis87@proton.me</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ewa.kolodziej@poczta.pl</t>
+          <t>ewa.kolodziej@outlook.com</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>a.kaczmarek@mail.pl</t>
+          <t>a.kaczmarek@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>piatek.monika@polaris-capital.pl</t>
+          <t>piatek.monika@icloud.com</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>mareksadowski@wp.pl</t>
+          <t>mareksadowski@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>barbara_wlodarczyk@gmail.com</t>
+          <t>barbara_wlodarczyk@wp.pl</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>rafal.borkowski93@proton.me</t>
+          <t>rafal.borkowski93@onet.pl</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>anna.kowalska@astra-finance.pl</t>
+          <t>anna.kowalska@interia.pl</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>t.nowacki@poczta.pl</t>
+          <t>t.nowacki@o2.pl</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>wisniewska.katarzyna@mail.pl</t>
+          <t>wisniewska.katarzyna@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>krzysztofwojcik@onet.pl</t>
+          <t>krzysztofwojcik@outlook.com</t>
         </is>
       </c>
     </row>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ewa_kowalczyk@nova-data.pl</t>
+          <t>ewa_kowalczyk@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>adam.kaminski70@gmail.com</t>
+          <t>adam.kaminski70@icloud.com</t>
         </is>
       </c>
     </row>
@@ -11249,7 +11249,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>m.zielinski@biuro.pl</t>
+          <t>m.zielinski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>szymanska.barbara@silesia-invest.pl</t>
+          <t>szymanska.barbara@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>rafaldabrowski@mail.pl</t>
+          <t>rafaldabrowski@onet.pl</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>anna_mazur@onet.pl</t>
+          <t>anna_mazur@interia.pl</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>tomasz.krawczyk76@wp.pl</t>
+          <t>tomasz.krawczyk76@o2.pl</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>katarzyna.wozniak@helios-markets.pl</t>
+          <t>katarzyna.wozniak@proton.me</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>k.jankowski@proton.me</t>
+          <t>k.jankowski@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>grabowska.ewa@biuro.pl</t>
+          <t>grabowska.ewa@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>adampawlak@poczta.pl</t>
+          <t>adampawlak@icloud.com</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>monika_michalska@polaris-capital.pl</t>
+          <t>monika_michalska@gmail.com</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>marek.krol82@onet.pl</t>
+          <t>marek.krol82@wp.pl</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>barbara.wieczorek@wp.pl</t>
+          <t>barbara.wieczorek@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>r.jablonski@gmail.com</t>
+          <t>r.jablonski@interia.pl</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>witkowska.anna@astra-finance.pl</t>
+          <t>witkowska.anna@o2.pl</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>tomaszwalczak@biuro.pl</t>
+          <t>tomaszwalczak@proton.me</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>katarzyna_stepien@poczta.pl</t>
+          <t>katarzyna_stepien@outlook.com</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>krzysztof.baran88@mail.pl</t>
+          <t>krzysztof.baran88@@wp.pl</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ewa.rutkowska@nova-data.pl</t>
+          <t>ewa.rutkowska@icloud.com</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>a.gorski@wp.pl</t>
+          <t>a.gorski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>sikora.monika@gmail.com</t>
+          <t>sikora.monika@wp.pl</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>marekostrowski@proton.me</t>
+          <t>marekostrowski@onet.pl</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>barbara_tomaszewska@silesia-invest.pl</t>
+          <t>barbara_tomaszewska@mail_invalid.pl</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>rafal.zajac94@poczta.pl</t>
+          <t>rafal.zajac94@o2.pl</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>anna.pietrzak@mail.pl</t>
+          <t>anna.pietrzak@proton.me</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>t.wojcicki@onet.pl</t>
+          <t>t.wojcicki@outlook.com</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>czarnecka.katarzyna@helios-markets.pl</t>
+          <t>czarnecka.katarzyna.gmail.com</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>krzysztoflis@gmail.com</t>
+          <t>krzysztoflis@icloud.com</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ewa_kolodziej@proton.me</t>
+          <t>ewa_kolodziej@gmail.com</t>
         </is>
       </c>
     </row>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>adam.kaczmarek71@biuro.pl</t>
+          <t>adam.kaczmarek71@wp.pl</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>monika.piatek@polaris-capital.pl</t>
+          <t>monika.piatek@onet.pl</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>m.sadowski@mail.pl</t>
+          <t>m.sadowski@nieistniejaca-domena</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>wlodarczyk.barbara@onet.pl</t>
+          <t>wlodarczyk.barbara@o2.pl</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>rafalborkowski@wp.pl</t>
+          <t>rafalborkowski@proton.me</t>
         </is>
       </c>
     </row>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>anna_kowalska@astra-finance.pl</t>
+          <t>anna_kowalska@outlook.com</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>tomasz.nowacki77@proton.me</t>
+          <t>tomasz.nowacki77@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>katarzyna.wisniewska@biuro.pl</t>
+          <t>katarzyna.wisniewska.gmail.com</t>
         </is>
       </c>
     </row>
@@ -14381,7 +14381,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>k.wojcik@poczta.pl</t>
+          <t>k.wojcik@gmail.com</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>kowalczyk.ewa@nova-data.pl</t>
+          <t>kowalczyk.ewa@wp.pl</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>monika_lewandowska@wp.pl</t>
+          <t>monika_lewandowska@interia.pl</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>marek.zielinski83@gmail.com</t>
+          <t>marek.zielinski83@nieistniejaca-domena</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>barbara.szymanska@silesia-invest.pl</t>
+          <t>barbara.szymanska@proton.me</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>r.dabrowski@biuro.pl</t>
+          <t>r.dabrowski@outlook.com</t>
         </is>
       </c>
     </row>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>mazur.anna@poczta.pl</t>
+          <t>mazur.anna@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>tomaszkrawczyk@mail.pl</t>
+          <t>tomaszkrawczyk@icloud.com</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>katarzyna_wozniak@helios-markets.pl</t>
+          <t>katarzyna_wozniak.gmail.com</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>ewa.grabowska@gmail.com</t>
+          <t>ewa.grabowska@onet.pl</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>a.pawlak@proton.me</t>
+          <t>a.pawlak@interia.pl</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>michalska.monika@polaris-capital.pl</t>
+          <t>michalska.monika@o2.pl</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>marekkrol@poczta.pl</t>
+          <t>marekkrol@nieistniejaca-domena</t>
         </is>
       </c>
     </row>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>barbara_wieczorek@mail.pl</t>
+          <t>barbara_wieczorek@outlook.com</t>
         </is>
       </c>
     </row>
@@ -15773,7 +15773,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>rafal.jablonski95@onet.pl</t>
+          <t>rafal.jablonski95@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>anna.witkowska@astra-finance.pl</t>
+          <t>anna.witkowska@icloud.com</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>stepien.katarzyna@proton.me</t>
+          <t>stepien.katarzyna.gmail.com</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>krzysztofbaran@biuro.pl</t>
+          <t>krzysztofbaran@onet.pl</t>
         </is>
       </c>
     </row>
@@ -16208,7 +16208,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>ewa_rutkowska@nova-data.pl</t>
+          <t>ewa_rutkowska@interia.pl</t>
         </is>
       </c>
     </row>
@@ -16295,7 +16295,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>adam.gorski72@mail.pl</t>
+          <t>adam.gorski72@o2.pl</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>monika.sikora@onet.pl</t>
+          <t>monika.sikora@proton.me</t>
         </is>
       </c>
     </row>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>m.ostrowski@wp.pl</t>
+          <t>m.ostrowski@nieistniejaca-domena</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>tomaszewska.barbara@silesia-invest.pl</t>
+          <t>tomaszewska.barbara@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>rafalzajac@proton.me</t>
+          <t>rafalzajac@icloud.com</t>
         </is>
       </c>
     </row>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>anna_pietrzak@biuro.pl</t>
+          <t>anna_pietrzak@gmail.com</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>tomasz.wojcicki78@poczta.pl</t>
+          <t>tomasz.wojcicki78@wp.pl</t>
         </is>
       </c>
     </row>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>katarzyna.czarnecka@helios-markets.pl</t>
+          <t>katarzyna.czarnecka.gmail.com</t>
         </is>
       </c>
     </row>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>k.lis@onet.pl</t>
+          <t>k.lis@interia.pl</t>
         </is>
       </c>
     </row>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>kolodziej.ewa@wp.pl</t>
+          <t>kolodziej.ewa@o2.pl</t>
         </is>
       </c>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>adamkaczmarek@gmail.com</t>
+          <t>adamkaczmarek@proton.me</t>
         </is>
       </c>
     </row>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>monika_piatek@polaris-capital.pl</t>
+          <t>monika_piatek@outlook.com</t>
         </is>
       </c>
     </row>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>marek.sadowski84@biuro.pl</t>
+          <t>marek.sadowski84@nieistniejaca-domena</t>
         </is>
       </c>
     </row>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>barbara.wlodarczyk@poczta.pl</t>
+          <t>barbara.wlodarczyk@icloud.com</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>r.borkowski@mail.pl</t>
+          <t>r.borkowski@gmail.com</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/pesel.xlsx
+++ b/data/xlsx/pesel.xlsx
@@ -200,7 +200,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>anna.kowalska@wp.pl</t>
+          <t>anna.kowalska@uuu.ii</t>
         </is>
       </c>
     </row>
@@ -287,7 +287,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>t.nowacki@onet.pl</t>
+          <t>t.nowacki@qqq.zz</t>
         </is>
       </c>
     </row>
@@ -374,7 +374,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>wisniewska.katarzyna@brak-domeny</t>
+          <t>wisniewska.katarzyna@abc.yy</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>krzysztofwojcik@o2.pl</t>
+          <t>krzysztofwojcik@xxx.uu</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ewa_kowalczyk@proton.me</t>
+          <t>ewa_kowalczyk@bbb.ii</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>adam.kaminski95@outlook.com</t>
+          <t>adam.kaminski95@mmm.zz</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>monika.lewandowska@yahoo.com</t>
+          <t>monika.lewandowska@nnn.yy</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>m.zielinski@localhost</t>
+          <t>m.zielinski@kkk.uu</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>szymanska.barbara@gmail.com</t>
+          <t>szymanska.barbara@proton.me</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>rafaldabrowski@wp.pl</t>
+          <t>rafaldabrowski@outlook.com</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>anna_mazur@onet.pl</t>
+          <t>anna_mazur@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>tomasz.krawczyk72@interia.pl</t>
+          <t>tomasz.krawczyk72@icloud.com</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>katarzyna.wozniak@brak-domeny</t>
+          <t>katarzyna.wozniak@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>k.jankowski@proton.me</t>
+          <t>k.jankowski@wp.pl</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>grabowska.ewa@outlook.com</t>
+          <t>grabowska.ewa@onet.pl</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>adampawlak@yahoo.com</t>
+          <t>adampawlak@interia.pl</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>monika_michalska@icloud.com</t>
+          <t>monika_michalska@o2.pl</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>marek.krol78@localhost</t>
+          <t>marek.krol78@proton.me</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>barbara.wieczorek@wp.pl</t>
+          <t>barbara.wieczorek@outlook.com</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>r.jablonski@onet.pl</t>
+          <t>r.jablonski@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>witkowska.anna@interia.pl</t>
+          <t>witkowska.anna@icloud.com</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>tomaszwalczak@o2.pl</t>
+          <t>tomaszwalczak@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>katarzyna_stepien@brak-domeny</t>
+          <t>katarzyna_stepien@wp.pl</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>krzysztof.baran84@outlook.com</t>
+          <t>krzysztof.baran84@onet.pl</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ewa.rutkowska@yahoo.com</t>
+          <t>ewa.rutkowska@interia.pl</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>a.gorski@icloud.com</t>
+          <t>a.gorski@o2.pl</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>sikora.monika@gmail.com</t>
+          <t>sikora.monika@proton.me</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>marekostrowski@gmailcom</t>
+          <t>marekostrowski@outlook.com</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>barbara_tomaszewska@localhost</t>
+          <t>barbara_tomaszewska@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>rafal.zajac90@onet.pl</t>
+          <t>rafal.zajac90@icloud.com</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>anna.pietrzak@interia.pl</t>
+          <t>anna.pietrzak@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>t.wojcicki@o2.pl</t>
+          <t>t.wojcicki@wp.pl</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>czarnecka.katarzyna@proton.me</t>
+          <t>czarnecka.katarzyna@onet.pl</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>krzysztoflis@brak-domeny</t>
+          <t>krzysztoflis@interia.pl</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>ewa_kolodziej@yahoo.com</t>
+          <t>ewa_kolodziej@o2.pl</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>adam.kaczmarek96@icloud.com</t>
+          <t>adam.kaczmarek96@proton.me</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>monika.piatek@gmail.com</t>
+          <t>monika.piatek@outlook.com</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>m.sadowski@wp.pl</t>
+          <t>m.sadowski@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>wlodarczyk.barbara@localhost</t>
+          <t>wlodarczyk.barbara@icloud.com</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>rafalborkowski@interia.pl</t>
+          <t>rafalborkowski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>anna_kowalska@o2.pl</t>
+          <t>anna_kowalska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>tomasz.nowacki73@proton.me</t>
+          <t>tomasz.nowacki73@onet.pl</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>katarzyna.wisniewska@outlook.com</t>
+          <t>katarzyna.wisniewska@interia.pl</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>k.wojcik@brak-domeny</t>
+          <t>k.wojcik@o2.pl</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>kowalczyk.ewa@icloud.com</t>
+          <t>kowalczyk.ewa@proton.me</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>adamkaminski@gmail.com</t>
+          <t>adamkaminski@outlook.com</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>monika_lewandowska@wp.pl</t>
+          <t>monika_lewandowska@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>marek.zielinski79@onet.pl</t>
+          <t>marek.zielinski79@icloud.com</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>barbara.szymanska@localhost</t>
+          <t>barbara.szymanska@gmail.com</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>r.dabrowski@o2.pl</t>
+          <t>r.dabrowski@wp.pl</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>mazur.anna@proton.me</t>
+          <t>mazur.anna@onet.pl</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>tomaszkrawczyk@outlook.com</t>
+          <t>tomaszkrawczyk@interia.pl</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>katarzyna_wozniak@@wp.pl</t>
+          <t>katarzyna_wozniak@o2.pl</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>krzysztof.jankowski85@icloud.com</t>
+          <t>krzysztof.jankowski85@proton.me</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ewa.grabowska@gmail.com</t>
+          <t>ewa.grabowska@outlook.com</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>a.pawlak@wp.pl</t>
+          <t>a.pawlak@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>michalska.monika@onet.pl</t>
+          <t>michalska.monika@icloud.com</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>marekkrol@mail_invalid.pl</t>
+          <t>marekkrol@gmail.com</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>barbara_wieczorek@o2.pl</t>
+          <t>barbara_wieczorek@wp.pl</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>rafal.jablonski91@proton.me</t>
+          <t>rafal.jablonski91@onet.pl</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>anna.witkowska@outlook.com</t>
+          <t>anna.witkowska@interia.pl</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>t.walczak@yahoo.com</t>
+          <t>t.walczak@o2.pl</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>stepien.katarzyna@@wp.pl</t>
+          <t>stepien.katarzyna@proton.me</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>krzysztofbaran@gmail.com</t>
+          <t>krzysztofbaran@outlook.com</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ewa_rutkowska@wp.pl</t>
+          <t>ewa_rutkowska@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>adam.gorski97@onet.pl</t>
+          <t>adam.gorski97@icloud.com</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>monika.sikora@interia.pl</t>
+          <t>monika.sikora@gmail.com</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>m.ostrowski@mail_invalid.pl</t>
+          <t>m.ostrowski@wp.pl</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>tomaszewska.barbara@proton.me</t>
+          <t>tomaszewska.barbara@onet.pl</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>rafalzajac@outlook.com</t>
+          <t>rafalzajac@interia.pl</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>anna_pietrzak@yahoo.com</t>
+          <t>anna_pietrzak@o2.pl</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>tomasz.wojcicki74@icloud.com</t>
+          <t>tomasz.wojcicki74@proton.me</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>katarzyna.czarnecka@@wp.pl</t>
+          <t>katarzyna.czarnecka@outlook.com</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>k.lis@wp.pl</t>
+          <t>k.lis@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>kolodziej.ewa@onet.pl</t>
+          <t>kolodziej.ewa@icloud.com</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>adamkaczmarek@interia.pl</t>
+          <t>adamkaczmarek@gmail.com</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>monika_piatek@o2.pl</t>
+          <t>monika_piatek@wp.pl</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>marek.sadowski80@mail_invalid.pl</t>
+          <t>marek.sadowski80@onet.pl</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>barbara.wlodarczyk@outlook.com</t>
+          <t>barbara.wlodarczyk@interia.pl</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>r.borkowski@yahoo.com</t>
+          <t>r.borkowski@o2.pl</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>kowalska.anna@icloud.com</t>
+          <t>kowalska.anna@proton.me</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>tomasznowacki@gmail.com</t>
+          <t>tomasznowacki@outlook.com</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>katarzyna_wisniewska@@wp.pl</t>
+          <t>katarzyna_wisniewska@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>krzysztof.wojcik86@onet.pl</t>
+          <t>krzysztof.wojcik86@icloud.com</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ewa.kowalczyk@interia.pl</t>
+          <t>ewa.kowalczyk@gmail.com</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>a.kaminski@o2.pl</t>
+          <t>a.kaminski@wp.pl</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>lewandowska.monika@proton.me</t>
+          <t>lewandowska.monika@onet.pl</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>marekzielinski@mail_invalid.pl</t>
+          <t>marekzielinski@interia.pl</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>barbara_szymanska@yahoo.com</t>
+          <t>barbara_szymanska@o2.pl</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>rafal.dabrowski92@icloud.com</t>
+          <t>rafal.dabrowski92@proton.me</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>anna.mazur@gmail.com</t>
+          <t>anna.mazur@outlook.com</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>t.krawczyk@wp.pl</t>
+          <t>t.krawczyk@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>wozniak.katarzyna@@wp.pl</t>
+          <t>wozniak.katarzyna@icloud.com</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>krzysztofjankowski@interia.pl</t>
+          <t>krzysztofjankowski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ewa_grabowska@o2.pl</t>
+          <t>ewa_grabowska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>adam.pawlak98@proton.me</t>
+          <t>adam.pawlak98@onet.pl</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>monika.michalska@outlook.com</t>
+          <t>monika.michalska@interia.pl</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>m.krol@mail_invalid.pl</t>
+          <t>m.krol@o2.pl</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>wieczorek.barbara@icloud.com</t>
+          <t>wieczorek.barbara@proton.me</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>rafaljablonski@gmail.com</t>
+          <t>rafaljablonski@outlook.com</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>anna_witkowska@wp.pl</t>
+          <t>anna_witkowska@mmm.zz</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>tomasz.walczak75@onet.pl</t>
+          <t>tomasz.walczak75@nnn.yy</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>katarzyna.stepien@@wp.pl</t>
+          <t>katarzyna.stepien@kkk.uu</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>k.baran@o2.pl</t>
+          <t>k.baran@tmp.ii</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>rutkowska.ewa@proton.me</t>
+          <t>rutkowska.ewa@foo.zz</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>adamgorski@outlook.com</t>
+          <t>adamgorski@bar.yy</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>monika_sikora@yahoo.com</t>
+          <t>monika_sikora@zzz.uu</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>marek.ostrowski81@mail_invalid.pl</t>
+          <t>marek.ostrowski81@uuu.ii</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>barbara.tomaszewska@gmail.com</t>
+          <t>barbara.tomaszewska@outlook.com</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>r.zajac@wp.pl</t>
+          <t>r.zajac@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>pietrzak.anna@onet.pl</t>
+          <t>pietrzak.anna@icloud.com</t>
         </is>
       </c>
     </row>
@@ -9857,7 +9857,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>tomaszwojcicki@interia.pl</t>
+          <t>tomaszwojcicki@gmail.com</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>katarzyna_czarnecka@@wp.pl</t>
+          <t>katarzyna_czarnecka@wp.pl</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>krzysztof.lis87@proton.me</t>
+          <t>krzysztof.lis87@onet.pl</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ewa.kolodziej@outlook.com</t>
+          <t>ewa.kolodziej@interia.pl</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>a.kaczmarek@yahoo.com</t>
+          <t>a.kaczmarek@o2.pl</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>piatek.monika@icloud.com</t>
+          <t>piatek.monika@proton.me</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>mareksadowski@mail_invalid.pl</t>
+          <t>mareksadowski@outlook.com</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>barbara_wlodarczyk@wp.pl</t>
+          <t>barbara_wlodarczyk@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>rafal.borkowski93@onet.pl</t>
+          <t>rafal.borkowski93@icloud.com</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>anna.kowalska@interia.pl</t>
+          <t>anna.kowalska@gmail.com</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>t.nowacki@o2.pl</t>
+          <t>t.nowacki@wp.pl</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>wisniewska.katarzyna@@wp.pl</t>
+          <t>wisniewska.katarzyna@onet.pl</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>krzysztofwojcik@outlook.com</t>
+          <t>krzysztofwojcik@interia.pl</t>
         </is>
       </c>
     </row>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ewa_kowalczyk@yahoo.com</t>
+          <t>ewa_kowalczyk@o2.pl</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>adam.kaminski70@icloud.com</t>
+          <t>adam.kaminski70@proton.me</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>monika.lewandowskaproton.me</t>
+          <t>monika.lewandowskaproton.me@outlook.com</t>
         </is>
       </c>
     </row>
@@ -11249,7 +11249,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>m.zielinski@gmail.com</t>
+          <t>m.zielinski@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>szymanska.barbara@mail_invalid.pl</t>
+          <t>szymanska.barbara@icloud.com</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>rafaldabrowski@onet.pl</t>
+          <t>rafaldabrowski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>anna_mazur@interia.pl</t>
+          <t>anna_mazur@wp.pl</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>tomasz.krawczyk76@o2.pl</t>
+          <t>tomasz.krawczyk76@onet.pl</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>katarzyna.wozniak@proton.me</t>
+          <t>katarzyna.wozniak@interia.pl</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>k.jankowski@@wp.pl</t>
+          <t>k.jankowski@o2.pl</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>grabowska.ewa@yahoo.com</t>
+          <t>grabowska.ewa@proton.me</t>
         </is>
       </c>
     </row>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>adampawlak@icloud.com</t>
+          <t>adampawlak@outlook.com</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>monika_michalska@gmail.com</t>
+          <t>monika_michalska@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>marek.krol82@wp.pl</t>
+          <t>marek.krol82@icloud.com</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>barbara.wieczorek@mail_invalid.pl</t>
+          <t>barbara.wieczorek@gmail.com</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>r.jablonski@interia.pl</t>
+          <t>r.jablonski@wp.pl</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>witkowska.anna@o2.pl</t>
+          <t>witkowska.anna@onet.pl</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>tomaszwalczak@proton.me</t>
+          <t>tomaszwalczak@interia.pl</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>katarzyna_stepien@outlook.com</t>
+          <t>katarzyna_stepien@o2.pl</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>krzysztof.baran88@@wp.pl</t>
+          <t>krzysztof.baran88@proton.me</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ewa.rutkowska@icloud.com</t>
+          <t>ewa.rutkowska@outlook.com</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>a.gorski@gmail.com</t>
+          <t>a.gorski@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>sikora.monika@wp.pl</t>
+          <t>sikora.monika@icloud.com</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>marekostrowski@onet.pl</t>
+          <t>marekostrowski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>barbara_tomaszewska@mail_invalid.pl</t>
+          <t>barbara_tomaszewska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>rafal.zajac94@o2.pl</t>
+          <t>rafal.zajac94@onet.pl</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>anna.pietrzak@proton.me</t>
+          <t>anna.pietrzak@interia.pl</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>t.wojcicki@outlook.com</t>
+          <t>t.wojcicki@o2.pl</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>czarnecka.katarzyna.gmail.com</t>
+          <t>czarnecka.katarzyna.gmail.com@proton.me</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>krzysztoflis@icloud.com</t>
+          <t>krzysztoflis@outlook.com</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ewa_kolodziej@gmail.com</t>
+          <t>ewa_kolodziej@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>adam.kaczmarek71@wp.pl</t>
+          <t>adam.kaczmarek71@icloud.com</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>monika.piatek@onet.pl</t>
+          <t>monika.piatek@gmail.com</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>m.sadowski@nieistniejaca-domena</t>
+          <t>m.sadowski@wp.pl</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>wlodarczyk.barbara@o2.pl</t>
+          <t>wlodarczyk.barbara@onet.pl</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>rafalborkowski@proton.me</t>
+          <t>rafalborkowski@interia.pl</t>
         </is>
       </c>
     </row>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>anna_kowalska@outlook.com</t>
+          <t>anna_kowalska@o2.pl</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>tomasz.nowacki77@yahoo.com</t>
+          <t>tomasz.nowacki77@proton.me</t>
         </is>
       </c>
     </row>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>katarzyna.wisniewska.gmail.com</t>
+          <t>katarzyna.wisniewska.gmail.com@outlook.com</t>
         </is>
       </c>
     </row>
@@ -14381,7 +14381,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>k.wojcik@gmail.com</t>
+          <t>k.wojcik@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>kowalczyk.ewa@wp.pl</t>
+          <t>kowalczyk.ewa@icloud.com</t>
         </is>
       </c>
     </row>
@@ -14555,7 +14555,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>adamkaminski@onet.pl</t>
+          <t>adamkaminski@gmail.com</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>monika_lewandowska@interia.pl</t>
+          <t>monika_lewandowska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>marek.zielinski83@nieistniejaca-domena</t>
+          <t>marek.zielinski83@onet.pl</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>barbara.szymanska@proton.me</t>
+          <t>barbara.szymanska@interia.pl</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>r.dabrowski@outlook.com</t>
+          <t>r.dabrowski@o2.pl</t>
         </is>
       </c>
     </row>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>mazur.anna@yahoo.com</t>
+          <t>mazur.anna@proton.me</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>tomaszkrawczyk@icloud.com</t>
+          <t>tomaszkrawczyk@outlook.com</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>katarzyna_wozniak.gmail.com</t>
+          <t>katarzyna_wozniak.gmail.com@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>krzysztof.jankowski89@wp.pl</t>
+          <t>krzysztof.jankowski89@icloud.com</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>ewa.grabowska@onet.pl</t>
+          <t>ewa.grabowska@gmail.com</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>a.pawlak@interia.pl</t>
+          <t>a.pawlak@wp.pl</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>michalska.monika@o2.pl</t>
+          <t>michalska.monika@onet.pl</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>marekkrol@nieistniejaca-domena</t>
+          <t>marekkrol@interia.pl</t>
         </is>
       </c>
     </row>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>barbara_wieczorek@outlook.com</t>
+          <t>barbara_wieczorek@o2.pl</t>
         </is>
       </c>
     </row>
@@ -15773,7 +15773,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>rafal.jablonski95@yahoo.com</t>
+          <t>rafal.jablonski95@proton.me</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>anna.witkowska@icloud.com</t>
+          <t>anna.witkowska@outlook.com</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>t.walczak@gmail.com</t>
+          <t>t.walczak@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>stepien.katarzyna.gmail.com</t>
+          <t>stepien.katarzyna.gmail.com@icloud.com</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>krzysztofbaran@onet.pl</t>
+          <t>krzysztofbaran@gmail.com</t>
         </is>
       </c>
     </row>
@@ -16208,7 +16208,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>ewa_rutkowska@interia.pl</t>
+          <t>ewa_rutkowska@wp.pl</t>
         </is>
       </c>
     </row>
@@ -16295,7 +16295,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>adam.gorski72@o2.pl</t>
+          <t>adam.gorski72@onet.pl</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>monika.sikora@proton.me</t>
+          <t>monika.sikora@interia.pl</t>
         </is>
       </c>
     </row>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>m.ostrowski@nieistniejaca-domena</t>
+          <t>m.ostrowski@o2.pl</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>tomaszewska.barbara@yahoo.com</t>
+          <t>tomaszewska.barbara@proton.me</t>
         </is>
       </c>
     </row>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>rafalzajac@icloud.com</t>
+          <t>rafalzajac@outlook.com</t>
         </is>
       </c>
     </row>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>anna_pietrzak@gmail.com</t>
+          <t>anna_pietrzak@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>tomasz.wojcicki78@wp.pl</t>
+          <t>tomasz.wojcicki78@icloud.com</t>
         </is>
       </c>
     </row>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>katarzyna.czarnecka.gmail.com</t>
+          <t>katarzyna.czarnecka.gmail.com@gmail.com</t>
         </is>
       </c>
     </row>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>k.lis@interia.pl</t>
+          <t>k.lis@wp.pl</t>
         </is>
       </c>
     </row>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>kolodziej.ewa@o2.pl</t>
+          <t>kolodziej.ewa@onet.pl</t>
         </is>
       </c>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>adamkaczmarek@proton.me</t>
+          <t>adamkaczmarek@interia.pl</t>
         </is>
       </c>
     </row>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>monika_piatek@outlook.com</t>
+          <t>monika_piatek@o2.pl</t>
         </is>
       </c>
     </row>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>marek.sadowski84@nieistniejaca-domena</t>
+          <t>marek.sadowski84@proton.me</t>
         </is>
       </c>
     </row>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>barbara.wlodarczyk@icloud.com</t>
+          <t>barbara.wlodarczyk@outlook.com</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>r.borkowski@gmail.com</t>
+          <t>r.borkowski@yahoo.com</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/pesel.xlsx
+++ b/data/xlsx/pesel.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>90013128840</t>
+          <t>60021406849</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -135,17 +135,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Kowalska-Krawczyk</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Kowalska</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1990-01-31</t>
+          <t>1960-14-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -175,12 +175,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 121/61, 50-066 Wrocław</t>
+          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 121/61, 50-066 Wrocław</t>
+          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -200,14 +200,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>anna.kowalska@gmail.com</t>
+          <t>anna.kowalska.krawczyk@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>73121530231</t>
+          <t>61032108236</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -232,7 +232,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1973-12-15</t>
+          <t>19610321</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -262,17 +262,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ul Legnicka 138, 54-203 Wrocław</t>
+          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ul Legnicka 138, 54-203 Wrocław</t>
+          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>UXR609746</t>
+          <t>ONV883946</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -294,7 +294,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>76100631581</t>
+          <t>62042809586</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -319,7 +319,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1976-10-06</t>
+          <t>28/04/1962</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -349,17 +349,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 155, 61-806 Poznań</t>
+          <t>ulica Floriańska 35, 31-019 Kraków</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 155, 61-806 Poznań</t>
+          <t>ulica Floriańska 35, 31-019 Kraków</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>XCC886289</t>
+          <t>RSG860489</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -381,7 +381,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02291432977</t>
+          <t>63050710972</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -406,7 +406,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2002-09-14</t>
+          <t>1963/07/05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -436,17 +436,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Głogowska 172, 60-734 Poznań</t>
+          <t>Długa 52, 31-147 Kraków</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Głogowska 172, 60-734 Poznań</t>
+          <t>Długa 52, 31-147 Kraków</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>AHN762832</t>
+          <t>UXR537032</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -468,7 +468,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>87070834328</t>
+          <t>64061412321</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1987-07-08</t>
+          <t>14-06-1964</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -523,17 +523,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ul. Długa 9/23, 80-831 Gdańsk</t>
+          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ul. Długa 9/23, 80-831 Gdańsk</t>
+          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>DMY639375</t>
+          <t>XCC413575</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>98021635714</t>
+          <t>65072113717</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1998-02-16</t>
+          <t>1965-21-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -610,17 +610,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 26, 80-236 Gdańsk</t>
+          <t>ul Zachodnia 86, 90-402 Łódź</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 26, 80-236 Gdańsk</t>
+          <t>ul Zachodnia 86, 90-402 Łódź</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GRJ415918</t>
+          <t>AHN990118</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -635,14 +635,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>adam.kaminski95@yahoo.com</t>
+          <t>adam.kaminski75@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>87071737064</t>
+          <t>66082815068</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1987-07-17</t>
+          <t>19660828</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 43, 70-435 Szczecin</t>
+          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 43, 70-435 Szczecin</t>
+          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>JWU792461</t>
+          <t>DMY266661</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -729,17 +729,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>67082638459</t>
+          <t>67090716451</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Mraek</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Michła</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1967-08-26</t>
+          <t>07/09/1967</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 60, 70-200 Szczecin</t>
+          <t>Legnicka 120, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 60, 70-200 Szczecin</t>
+          <t>Legnicka 120, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>MBF369004</t>
+          <t>GRJ343204</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>m.zielinski@o2.pl</t>
+          <t>m.zielinski@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>84041439801</t>
+          <t>68101417802</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1984-04-14</t>
+          <t>1968/14/10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ul. Mariacka 77/75, 40-014 Katowice</t>
+          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ul. Mariacka 77/75, 40-014 Katowice</t>
+          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -896,14 +896,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>szymanska.barbara@icloud.com</t>
+          <t>szymanska.barbara@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>83072941196</t>
+          <t>79112119190</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1983-07-29</t>
+          <t>21-11-1969</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>os. Warszawska 94, 40-009 Katowice</t>
+          <t>ul Głogowska 154, 60-734 Poznań</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>os. Warszawska 94, 40-009 Katowice</t>
+          <t>ul Głogowska 154, 60-734 Poznań</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SLB322090</t>
+          <t>MBF896290</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -983,14 +983,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>rafaldabrowski@uuu.ii</t>
+          <t>rafaldabrowski@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02310542546</t>
+          <t>70122820541</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2002-11-05</t>
+          <t>1970-28-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 111, 20-002 Lublin</t>
+          <t>ulica Długa 171, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 111, 20-002 Lublin</t>
+          <t>ulica Długa 171, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>VQM098633</t>
+          <t>PGQ272833</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1070,14 +1070,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>anna_mazur@outlook.com</t>
+          <t>anna_mazur@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>67112943935</t>
+          <t>71010721939</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1967-11-29</t>
+          <t>19710107</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Narutowicza 128, 20-004 Lublin</t>
+          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Narutowicza 128, 20-004 Lublin</t>
+          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>YVX675176</t>
+          <t>SLB549376</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1157,14 +1157,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>tomasz.krawczyk72@wp.pl</t>
+          <t>tomasz.krawczyk81@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00211045287</t>
+          <t>72021423289</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2000-01-10</t>
+          <t>14/02/1972</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ul. Lipowa 145/37, 15-424 Białystok</t>
+          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ul. Lipowa 145/37, 15-424 Białystok</t>
+          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BAI451719</t>
+          <t>VQM925919</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1244,14 +1244,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>katarzyna.wozniak@onet.pl</t>
+          <t>katarzyna.wozniak@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>82120546677</t>
+          <t>73032124675</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1982-12-05</t>
+          <t>1973/21/03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1306,17 +1306,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 162, 15-092 Białystok</t>
+          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 162, 15-092 Białystok</t>
+          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>EFT028262</t>
+          <t>YVX202462</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>k.jankowski@interia.pl</t>
+          <t>k.jankowski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>73030548026</t>
+          <t>74042826025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1973-03-05</t>
+          <t>28-04-1974</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ulica Gdańska 179, 85-005 Bydgoszcz</t>
+          <t>ulica Mariacka 59, 40-014 Katowice</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ulica Gdańska 179, 85-005 Bydgoszcz</t>
+          <t>ulica Mariacka 59, 40-014 Katowice</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>HKE804805</t>
+          <t>BAI679005</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>grabowska.ewa@yahoo.com</t>
+          <t>grabowska.ewa@proton.me</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>71021849411</t>
+          <t>75050727418</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1971-02-18</t>
+          <t>1975-07-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Dworcowa 16, 85-009 Bydgoszcz</t>
+          <t>Warszawska 76, 40-009 Katowice</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Dworcowa 16, 85-009 Bydgoszcz</t>
+          <t>Warszawska 76, 40-009 Katowice</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>KPP481348</t>
+          <t>EFT955548</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1505,14 +1505,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>adampawlak@proton.me</t>
+          <t>adampawlak@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>99022250768</t>
+          <t>76061428767</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1999-02-22</t>
+          <t>19760614</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ul. Szeroka 33/89, 87-100 Toruń</t>
+          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ul. Szeroka 33/89, 87-100 Toruń</t>
+          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1592,14 +1592,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>monika_michalska@o2.pl</t>
+          <t>monika_michalska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>79060652155</t>
+          <t>77072130157</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1979-06-06</t>
+          <t>21/07/1977</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ul Chełmińska 50, 87-100 Toruń</t>
+          <t>ul Narutowicza 110, 20-004 Lublin</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ul Chełmińska 50, 87-100 Toruń</t>
+          <t>ul Narutowicza 110, 20-004 Lublin</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>QZL834434</t>
+          <t>KPP308634</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1674,19 +1674,19 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>759944841</t>
+          <t/>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>marek.krol78@icloud.com</t>
+          <t>marek.krol87@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>66120353505</t>
+          <t>78082831506</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1966-12-03</t>
+          <t>1978/28/08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 67, 35-030 Rzeszów</t>
+          <t>ulica Lipowa 127, 15-424 Białystok</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 67, 35-030 Rzeszów</t>
+          <t>ulica Lipowa 127, 15-424 Białystok</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>TEW310977</t>
+          <t>NUA385177</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1766,14 +1766,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>barbara.wieczorek@gmail.com</t>
+          <t>barbara.wieczorek@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>67051254895</t>
+          <t>79090732890</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1967-05-12</t>
+          <t>07-09-1979</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>WJH487520</t>
+          <t>QZL461720</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1853,14 +1853,14 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>r.jablonski@qqq.zz</t>
+          <t>r.jablonski@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>73072356247</t>
+          <t>80101434241</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1973-07-23</t>
+          <t>1980-14-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1915,17 +1915,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 101/51, 25-007 Kielce</t>
+          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 101/51, 25-007 Kielce</t>
+          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ZOS064063</t>
+          <t>TEW538263</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1940,14 +1940,14 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>witkowska.anna@wp.pl</t>
+          <t>witkowska.anna@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>85051057638</t>
+          <t>81112135637</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1985-05-10</t>
+          <t>19811121</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 25-512 Kielce</t>
+          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 25-512 Kielce</t>
+          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>CTD640606</t>
+          <t>WJH314806</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2027,14 +2027,14 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>tomaszwalczak@onet.pl</t>
+          <t>tomaszwalczak@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>76122058988</t>
+          <t>82122836987</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1976-12-20</t>
+          <t>28/12/1982</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 135, 10-504 Olsztyn</t>
+          <t>ulica Szeroka 15, 87-100 Toruń</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 135, 10-504 Olsztyn</t>
+          <t>ulica Szeroka 15, 87-100 Toruń</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>FYO517149</t>
+          <t>ZOS991349</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2114,14 +2114,14 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>katarzyna_stepien@interia.pl</t>
+          <t>katarzyna_stepien@proton.me</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>85021860378</t>
+          <t>83010738376</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1985-02-18</t>
+          <t>1983/07/01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 152, 10-540 Olsztyn</t>
+          <t>Chełmińska 32, 87-100 Toruń</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 152, 10-540 Olsztyn</t>
+          <t>Chełmińska 32, 87-100 Toruń</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>IDZ793692</t>
+          <t>CTD467892</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2201,14 +2201,14 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>krzysztof.baran84@yahoo.com</t>
+          <t>krzysztof.baran93@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>94110961722</t>
+          <t>84021439724</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1994-11-09</t>
+          <t>14-02-1984</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ul. Krakowska 169/13, 45-018 Opole</t>
+          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>ul. Krakowska 169/13, 45-018 Opole</t>
+          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2288,14 +2288,14 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ewa.rutkowska@proton.me</t>
+          <t>ewa.rutkowska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>86092963111</t>
+          <t>85032141114</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1986-09-29</t>
+          <t>1985-21-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ul Ozimska 6, 45-057 Opole</t>
+          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ul Ozimska 6, 45-057 Opole</t>
+          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ONV446778</t>
+          <t>IDZ620978</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2375,14 +2375,14 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>a.gorski@o2.pl</t>
+          <t>a.gorski@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>98061564467</t>
+          <t>86042842464</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1998-06-15</t>
+          <t>19860428</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 23, 65-034 Zielona Góra</t>
+          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 23, 65-034 Zielona Góra</t>
+          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>RSG223321</t>
+          <t>LIK797521</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>sikora.monika@icloud.com</t>
+          <t>sikora.monika@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>70110365858</t>
+          <t>87050743857</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1970-11-03</t>
+          <t>07/05/1987</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Kupiecka 40, 65-058 Zielona Góra</t>
+          <t>Warszawska 100, 25-512 Kielce</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Kupiecka 40, 65-058 Zielona Góra</t>
+          <t>Warszawska 100, 25-512 Kielce</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>UXR899864</t>
+          <t>ONV374064</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2549,14 +2549,14 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>marekostrowski@gmail.com</t>
+          <t>marekostrowski@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>95012567203</t>
+          <t>88061445206</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1995-01-25</t>
+          <t>1988/14/06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 57/65, 81-372 Gdynia</t>
+          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 57/65, 81-372 Gdynia</t>
+          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>XCC176407</t>
+          <t>RSG250607</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>barbara_tomaszewska@outlook.com</t>
+          <t>barbara_tomaszewska@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>81040168594</t>
+          <t>89072146593</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1981-04-01</t>
+          <t>21-07-1989</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2698,17 +2698,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ul 10 Lutego 74, 81-364 Gdynia</t>
+          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>ul 10 Lutego 74, 81-364 Gdynia</t>
+          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>AHN952950</t>
+          <t>UXR727150</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>rafal.zajac90@abc.yy</t>
+          <t>rafal.zajac70@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>68012869941</t>
+          <t>92082869943</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1968-01-28</t>
+          <t>1992-28-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2810,14 +2810,14 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>anna.pietrzak@onet.pl</t>
+          <t>anna.pietrzak@proton.me</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>79060471330</t>
+          <t>93090771330</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1979-06-04</t>
+          <t>19930907</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2897,14 +2897,14 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>t.wojcicki@interia.pl</t>
+          <t>t.wojcicki@yahoocom</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>83062072680</t>
+          <t>94101472682</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1983-06-20</t>
+          <t>14/10/1994</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2984,14 +2984,14 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>czarnecka.katarzyna@yahoo.com</t>
+          <t>czarnecka.katarzyna@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>83080874071</t>
+          <t>95112174079</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1983-08-08</t>
+          <t>1995/21/11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3071,14 +3071,14 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>krzysztoflis@proton.me</t>
+          <t>krzysztoflis@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>87021975421</t>
+          <t>96122875428</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1987-02-19</t>
+          <t>28-12-1996</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>ewa_kolodziej@o2.pl</t>
+          <t>ewa_kolodziej@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>67100476810</t>
+          <t>97010776816</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1967-10-04</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3245,14 +3245,14 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>adam.kaczmarek96@icloud.com</t>
+          <t>adam.kaczmarek96@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>66070378164</t>
+          <t>98021478166</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1966-07-03</t>
+          <t>19980214</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3332,14 +3332,14 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>monika.piatek@gmail.com</t>
+          <t>monika.piatek@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>82081079553</t>
+          <t>99032179552</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1982-08-10</t>
+          <t>21/03/1999</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3419,14 +3419,14 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>m.sadowski@outlook.com</t>
+          <t>m.sadowski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>03261880903</t>
+          <t>00242880909</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2003-06-18</t>
+          <t>2000/28/04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>wlodarczyk.barbara@wp.pl</t>
+          <t>wlodarczyk.barbara@proton.me</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>97120382293</t>
+          <t>01250782294</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1997-12-03</t>
+          <t>07-05-2001</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3593,14 +3593,14 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>rafalborkowski@xxx.uu</t>
+          <t>rafalborkowski@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>74091983641</t>
+          <t>02261483642</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3615,17 +3615,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Kowalska-Krawczyk</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Kowalska</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Dąbrowska</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1974-09-19</t>
+          <t>2002-14-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>anna_kowalska@interia.pl</t>
+          <t>anna_kowalska.krawczyk@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>84021285035</t>
+          <t>03272185039</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1984-02-12</t>
+          <t>20030721</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3767,14 +3767,14 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>tomasz.nowacki73@yahoo.com</t>
+          <t>tomasz.nowacki73@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>94060386389</t>
+          <t>04282886389</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1994-06-03</t>
+          <t>28/08/2004</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3854,14 +3854,14 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>katarzyna.wisniewska@proton.me</t>
+          <t>katarzyna.wisniewska@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>98051787773</t>
+          <t>05290787772</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1998-05-17</t>
+          <t>2005/07/09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>k.wojcik@o2.pl</t>
+          <t>k.wojcik@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>75022889120</t>
+          <t>60101489120</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1975-02-28</t>
+          <t>14-10-1960</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4028,14 +4028,14 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>kowalczyk.ewa@icloud.com</t>
+          <t>kowalczyk.ewa@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>74040590519</t>
+          <t>61112190519</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1974-04-05</t>
+          <t>1961-21-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4115,14 +4115,14 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>adamkaminski@gmail.com</t>
+          <t>adamkaminski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>85050191861</t>
+          <t>62122891869</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1985-05-01</t>
+          <t>19621228</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>monika_lewandowska@outlook.com</t>
+          <t>monika_lewandowska@proton.me</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>02292293254</t>
+          <t>63010793258</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2002-09-22</t>
+          <t>07/01/1963</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4289,14 +4289,14 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>marek.zielinski79@wp.pl</t>
+          <t>marek.zielinski79@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>66120494604</t>
+          <t>64021494606</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1966-12-04</t>
+          <t>1964/14/02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4376,14 +4376,14 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>barbara.szymanska@onet.pl</t>
+          <t>barbara.szymanska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00232595998</t>
+          <t>65032195993</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2000-03-25</t>
+          <t>21-03-1965</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>r.dabrowski@bbb.ii</t>
+          <t>r.dabrowski@finanse24.xs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>96031097344</t>
+          <t>66042897343</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Jabłońska-Ostrowska</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1996-03-10</t>
+          <t>1966-28-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4550,14 +4550,14 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>mazur.anna@yahoo.com</t>
+          <t>mazur.anna@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>80122598739</t>
+          <t>67050798736</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1980-12-25</t>
+          <t>19670507</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>tomaszkrawczyk@proton.me</t>
+          <t>tomaszkrawczyk@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00210300084</t>
+          <t>68061400089</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2000-01-03</t>
+          <t>14/06/1968</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4724,14 +4724,14 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>katarzyna_wozniak@o2.pl</t>
+          <t>katarzyna_wozniak@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>77062101479</t>
+          <t>69072101475</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1977-06-21</t>
+          <t>1969/21/07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4811,14 +4811,14 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>krzysztof.jankowski85@icloud.com</t>
+          <t>krzysztof.jankowski85@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>86010702822</t>
+          <t>70082802823</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1986-01-07</t>
+          <t>28-08-1970</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4898,14 +4898,14 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ewa.grabowska@gmail.com</t>
+          <t>ewa.grabowska@proton.me</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>80122504219</t>
+          <t>71090704217</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1980-12-25</t>
+          <t>1971-07-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>a.pawlak@outlook.com</t>
+          <t>a.pawlak@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>70032005566</t>
+          <t>72101405569</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1970-03-20</t>
+          <t>19721014</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5072,14 +5072,14 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>michalska.monika@wp.pl</t>
+          <t>michalska.monika@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>96120306951</t>
+          <t>73112106955</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1996-12-03</t>
+          <t>21/11/1973</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>iKelec</t>
+          <t>ieKlec</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5159,14 +5159,14 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>marekkrol@onet.pl</t>
+          <t>marekkrol@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>75052208300</t>
+          <t>74122808305</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1975-05-22</t>
+          <t>1974/28/12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5246,14 +5246,14 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>barbara_wieczorek@interia.pl</t>
+          <t>barbara_wieczorek@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>81082709691</t>
+          <t>85010709694</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1971-08-27</t>
+          <t>07-01-1975</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5333,14 +5333,14 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>rafal.jablonski91@uuu.ii</t>
+          <t>rafal.jablonski91@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>74061511043</t>
+          <t>76021411046</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1974-06-15</t>
+          <t>1976-14-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5420,14 +5420,14 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>anna.witkowska@proton.me</t>
+          <t>anna.witkowska@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>82072312434</t>
+          <t>77032112432</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5514,7 +5514,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>88011313784</t>
+          <t>78042813782</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1988-01-13</t>
+          <t>28/04/1978</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5594,14 +5594,14 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>stepien.katarzyna@icloud.com</t>
+          <t>stepien.katarzyna@proton.me</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>88032915178</t>
+          <t>79050715176</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1988-03-29</t>
+          <t>1979/07/05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5681,14 +5681,14 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>krzysztofbaran@gmail.com</t>
+          <t>krzysztofbaran@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>89071816525</t>
+          <t>80061416523</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1989-07-18</t>
+          <t>14-06-1980</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5768,14 +5768,14 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ewa_rutkowska@outlook.com</t>
+          <t>ewa_rutkowska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>65070417912</t>
+          <t>81072117919</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1965-07-04</t>
+          <t>1981-21-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5855,14 +5855,14 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>adam.gorski97@wp.pl</t>
+          <t>adam.gorski97@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>95100619263</t>
+          <t>82082819260</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1995-10-06</t>
+          <t>1982-08-28T07:55:19Z</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5942,14 +5942,14 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>monika.sikora@onet.pl</t>
+          <t>monika.sikora@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>93041520655</t>
+          <t>83090720656</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1993-04-15</t>
+          <t>07/09/1983</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6029,14 +6029,14 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>m.ostrowski@interia.pl</t>
+          <t>m.ostrowski@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>88082422000</t>
+          <t>84101422008</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1988-08-24</t>
+          <t>1984/14/10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6116,14 +6116,14 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>tomaszewska.barbara@yahoo.com</t>
+          <t>tomaszewska.barbara@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>98120323392</t>
+          <t>85112123395</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1998-12-03</t>
+          <t>21-11-1985</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6203,14 +6203,14 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>rafalzajac@qqq.zz</t>
+          <t>rafalzajac@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>75012024748</t>
+          <t>86122824744</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1975-01-20</t>
+          <t>1986-28-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6290,14 +6290,14 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>anna_pietrzak@o2.pl</t>
+          <t>anna_pietrzak@proton.me</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>91061026135</t>
+          <t>87010726133</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1991-06-10</t>
+          <t>19870107</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6377,14 +6377,14 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>tomasz.wojcicki74@icloud.com</t>
+          <t>tomasz.wojcicki74@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>65020127483</t>
+          <t>88021427482</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1965-02-01</t>
+          <t>14/02/1988</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>95082128874</t>
+          <t>89032128878</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1995-08-21</t>
+          <t>1989/21/03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6558,7 +6558,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>70100530222</t>
+          <t>90042830220</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1970-10-05</t>
+          <t>28-04-1990</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6645,7 +6645,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>98052831617</t>
+          <t>91050731613</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1998-05-28</t>
+          <t>1991-07-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6732,7 +6732,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>73073032962</t>
+          <t>92061432962</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1973-07-30</t>
+          <t>19920614</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>LIK250471</t>
+          <t/>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>97030434356</t>
+          <t>93072134359</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1997-03-04</t>
+          <t>21/07/1993</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6899,14 +6899,14 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>marek.sadowski80@yahoo.com</t>
+          <t>marek.sadowski80@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>80032935703</t>
+          <t>94082835708</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1980-03-29</t>
+          <t>1994/28/08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6993,7 +6993,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>74051937097</t>
+          <t>95090737093</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1974-05-19</t>
+          <t>07-09-1995</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7073,14 +7073,14 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>r.borkowski@abc.yy</t>
+          <t>r.borkowski@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>68073138442</t>
+          <t>96101438444</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7095,17 +7095,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1968-07-31</t>
+          <t>1996-14-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7160,14 +7160,14 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>kowalska.anna@icloud.com</t>
+          <t>kowalska.krawczyk.anna@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>96083039839</t>
+          <t>97112139830</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1996-08-30</t>
+          <t>19971121</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>tomasznowacki@gmail.com</t>
+          <t>tomasznowacki@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>02303041188</t>
+          <t>98122841184</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2002-10-30</t>
+          <t>28/12/1998</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t/>
+          <t>K</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7329,19 +7329,19 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>+48 510 692 520</t>
+          <t/>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>katarzyna_wisniewska@outlook.com</t>
+          <t>katarzyna_wisniewska@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>78112542574</t>
+          <t>99010742572</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1978-11-25</t>
+          <t>1999/07/01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7421,14 +7421,14 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>krzysztof.wojcik86@wp.pl</t>
+          <t>krzysztof.wojcik86@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>70070543925</t>
+          <t>00221443925</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1970-07-05</t>
+          <t>14-02-2000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>JWU762815</t>
+          <t>JWU862815</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7508,14 +7508,14 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ewa.kowalczyk@onet.pl</t>
+          <t>ewa.kowalczyk@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>74073145313</t>
+          <t>01232145312</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1974-07-31</t>
+          <t>2001-21-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7595,14 +7595,14 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>a.kaminski@interia.pl</t>
+          <t>a.kaminski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>89062246667</t>
+          <t>02242846662</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
+          <t>20020428</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7682,14 +7682,14 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>lewandowska.monika@yahoo.com</t>
+          <t>lewandowska.monika@proton.me</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>78032348056</t>
+          <t>03250748056</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1978-03-23</t>
+          <t>07/05/2003</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>marekzielinski@proton.me</t>
+          <t>marekzielinski@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>95102049404</t>
+          <t>04261449404</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1995-10-20</t>
+          <t>2004/14/06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7856,14 +7856,14 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>barbara_szymanska@o2.pl</t>
+          <t>barbara_szymanska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>91072550799</t>
+          <t>05272150794</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1991-07-25</t>
+          <t>21-07-2005</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7943,14 +7943,14 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>rafal.dabrowski92@xxx.uu</t>
+          <t>rafal.dabrowski92@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>71060952143</t>
+          <t>60082852140</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1971-06-09</t>
+          <t>1960-28-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8030,14 +8030,14 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>anna.mazur@gmail.com</t>
+          <t>anna.mazur@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>83043053538</t>
+          <t>61090753533</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1983-04-30</t>
+          <t>19610907</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8117,14 +8117,14 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>t.krawczyk@outlook.com</t>
+          <t>t.krawczyk@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>94061854887</t>
+          <t>62101454885</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1994-06-18</t>
+          <t>14/10/1962</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8204,14 +8204,14 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>wozniak.katarzyna@wp.pl</t>
+          <t>wozniak.katarzyna@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>83021856278</t>
+          <t>63112156272</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1983-02-18</t>
+          <t>1963/21/11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8291,14 +8291,14 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>krzysztofjankowski@onet.pl</t>
+          <t>krzysztofjankowski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>02251757623</t>
+          <t>64122857621</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2002-05-17</t>
+          <t>28-12-1964</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>NUA528245</t>
+          <t>NUA428245</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8378,14 +8378,14 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ewa_grabowska@interia.pl</t>
+          <t>ewa_grabowska@proton.me</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>00230259014</t>
+          <t>65010759010</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2000-03-02</t>
+          <t>1965-07-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8472,7 +8472,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>77102660362</t>
+          <t>66021460362</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1977-10-26</t>
+          <t>19660214</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8552,14 +8552,14 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>monika.michalska@proton.me</t>
+          <t>monika.michalska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>79010961757</t>
+          <t>67032161758</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1979-01-09</t>
+          <t>21/03/1967</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>m.krol@o2.pl</t>
+          <t>m.krol@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>70072663100</t>
+          <t>68042863108</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1970-07-26</t>
+          <t>1968/28/04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8726,14 +8726,14 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>wieczorek.barbara@icloud.com</t>
+          <t>wieczorek.barbara@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>81011264494</t>
+          <t>69050764492</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1981-01-12</t>
+          <t>07-05-1969</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8813,14 +8813,14 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>rafaljablonski@bbb.ii</t>
+          <t>rafaljablonski@ubezpiecznia.pl</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>79072565849</t>
+          <t>70061465849</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1979-07-25</t>
+          <t>1970-14-06</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8900,14 +8900,14 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>anna_witkowska@outlook.com</t>
+          <t>anna_witkowska@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>78021267238</t>
+          <t>71072167236</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1978-02-12</t>
+          <t>19710721</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8987,14 +8987,14 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>tomasz.walczak75@wp.pl</t>
+          <t>tomasz.walczak75@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>71070968587</t>
+          <t>72082868586</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1971-07-09</t>
+          <t>28/08/1972</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>katarzyna.stepien@onet.pl</t>
+          <t>katarzyna.stepien@proton.me</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>00300569971</t>
+          <t>73090769979</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2000-10-05</t>
+          <t>1973/07/09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9161,14 +9161,14 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>k.baran@interia.pl</t>
+          <t>k.baran@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>85081871323</t>
+          <t>74101471324</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1985-08-18</t>
+          <t>14-10-1974</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9248,14 +9248,14 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>rutkowska.ewa@yahoo.com</t>
+          <t>rutkowska.ewa@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>80082472719</t>
+          <t>75112172710</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1980-08-24</t>
+          <t>1975-21-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9335,14 +9335,14 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>adamgorski@proton.me</t>
+          <t>adamgorski@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>66102174061</t>
+          <t>76122874061</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1966-10-21</t>
+          <t>19761228</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9422,19 +9422,19 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>monika_sikora@o2.pl</t>
+          <t>monika_sikora@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>70111375454</t>
+          <t>77010775459</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Marke</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1970-11-13</t>
+          <t>07/01/1977</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9509,14 +9509,14 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>marek.ostrowski81@icloud.com</t>
+          <t>marek.ostrowski81@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>86041676808</t>
+          <t>78021476807</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1986-04-16</t>
+          <t>1978/14/02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9596,14 +9596,14 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>barbara.tomaszewska@gmail.com</t>
+          <t>barbara.tomaszewska@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>78061378196</t>
+          <t>89032178195</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1978-06-13</t>
+          <t>21-03-1979</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9683,14 +9683,14 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>r.zajac@uuu.ii</t>
+          <t>r.zajac@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>02280479549</t>
+          <t>80042879543</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2002-08-04</t>
+          <t>1980-28-04</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9770,14 +9770,14 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>pietrzak.anna@wp.pl</t>
+          <t>pietrzak.anna@proton.me</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>87091280939</t>
+          <t>81050780939</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1987-09-12</t>
+          <t>19810507</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -9857,14 +9857,14 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>tomaszwojcicki@onet.pl</t>
+          <t>tomaszwojcicki@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>65100582287</t>
+          <t>82061482289</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1965-10-05</t>
+          <t>14/06/1982</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -9944,14 +9944,14 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>katarzyna_czarnecka@interia.pl</t>
+          <t>katarzyna_czarnecka@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>83012783671</t>
+          <t>83072183675</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1983-01-27</t>
+          <t>1983/21/07</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10031,14 +10031,14 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>krzysztof.lis87@yahoo.com</t>
+          <t>krzysztof.lis87@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>97122485024</t>
+          <t>84082885025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1997-12-24</t>
+          <t>28-08-1984</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10118,14 +10118,14 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ewa.kolodziej@proton.me</t>
+          <t>ewa.kolodziej@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>04291886411</t>
+          <t>85090786418</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2004-09-18</t>
+          <t>1985-07-09</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10205,14 +10205,14 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>a.kaczmarek@o2.pl</t>
+          <t>a.kaczmarek@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>67012387769</t>
+          <t>86101487760</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1967-01-23</t>
+          <t>19861014</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10292,14 +10292,14 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>piatek.monika@icloud.com</t>
+          <t>piatek.monika@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>85072989152</t>
+          <t>87112189157</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1985-07-29</t>
+          <t>21/11/1987</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10379,14 +10379,14 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>mareksadowski@gmail.com</t>
+          <t>mareksadowski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>67031990500</t>
+          <t>88122890509</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1967-03-19</t>
+          <t>1988/28/12</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10466,14 +10466,14 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>barbara_wlodarczyk@outlook.com</t>
+          <t>barbara_wlodarczyk@proton.me</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>68071991892</t>
+          <t>89010791898</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1968-07-19</t>
+          <t>07-01-1989</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10553,14 +10553,14 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>rafal.borkowski93@qqq.zz</t>
+          <t>rafal.borkowski93@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>83112193248</t>
+          <t>90021493246</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10575,17 +10575,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>Kowalska-Krawczyk</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>Kowalska</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1983-11-21</t>
+          <t>1990-14-02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10640,14 +10640,14 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>anna.kowalska@onet.pl</t>
+          <t>anna.kowalska.krawczyk@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>79050394638</t>
+          <t>91032194632</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1979-05-03</t>
+          <t>19910321</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10727,14 +10727,14 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>t.nowacki@interia.pl</t>
+          <t>t.nowacki@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>74111695985</t>
+          <t>92042895982</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1974-11-16</t>
+          <t>28/04/1992</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -10814,14 +10814,14 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>wisniewska.katarzyna@yahoo.com</t>
+          <t>wisniewska.katarzyna@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>74032097372</t>
+          <t>93050797376</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1974-03-20</t>
+          <t>1993/07/05</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10901,14 +10901,14 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>krzysztofwojcik@proton.me</t>
+          <t>krzysztofwojcik@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>79041798720</t>
+          <t>94061498724</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1979-04-17</t>
+          <t>14-06-1994</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -10988,14 +10988,14 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ewa_kowalczyk@o2.pl</t>
+          <t>ewa_kowalczyk@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>68031200112</t>
+          <t>95072100114</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1968-03-12</t>
+          <t>1995-21-07</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11075,14 +11075,14 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>adam.kaminski70@icloud.com</t>
+          <t>adam.kaminski70@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>66040701468</t>
+          <t>96082801464</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1966-04-07</t>
+          <t>19960828</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11162,14 +11162,14 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>monika.lewandowskaproton.me@gmail.com</t>
+          <t>monika.lewandowska@proton.me</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>71091702856</t>
+          <t>97090702857</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1971-09-17</t>
+          <t>07/09/1997</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11249,14 +11249,14 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>m.zielinski@outlook.com</t>
+          <t>m.zielinski@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>97031104201</t>
+          <t>98101404209</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1997-03-11</t>
+          <t>1998/14/10</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11336,14 +11336,14 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>szymanska.barbara@wp.pl</t>
+          <t>szymanska.barbara@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>99121205595</t>
+          <t>99112105596</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1999-12-12</t>
+          <t>21-11-1999</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11423,14 +11423,14 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>rafaldabrowski@abc.yy</t>
+          <t>rafaldabrowski@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>77122406948</t>
+          <t>00322806940</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1977-12-24</t>
+          <t>2000-28-12</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11510,14 +11510,14 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>anna_mazur@interia.pl</t>
+          <t>anna_mazur@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>68072608333</t>
+          <t>01210708339</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1968-07-26</t>
+          <t>20010107</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11597,14 +11597,14 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>tomasz.krawczyk76@yahoo.com</t>
+          <t>tomasz.krawczyk76onet.pl</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>02293009685</t>
+          <t>02221409688</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2002-09-30</t>
+          <t>14/02/2002</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11684,14 +11684,14 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>katarzyna.wozniak@proton.me</t>
+          <t>katarzyna.wozniak@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>71111411074</t>
+          <t>03232111078</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1971-11-14</t>
+          <t>2003/21/03</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11778,7 +11778,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>00243012422</t>
+          <t>04242812427</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2000-04-30</t>
+          <t>28-04-2004</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -11858,14 +11858,14 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>grabowska.ewa@icloud.com</t>
+          <t>grabowska.ewa@proton.me</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>74030413817</t>
+          <t>05250713810</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>1974-03-04</t>
+          <t>2005-07-05</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -11945,14 +11945,14 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>adampawlak@gmail.com</t>
+          <t>adampawlak@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>81072515168</t>
+          <t>60061415166</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1981-07-25</t>
+          <t>19600614</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12032,14 +12032,14 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>monika_michalska@outlook.com</t>
+          <t>monika_michalska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>94042016550</t>
+          <t>61072116552</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1994-04-20</t>
+          <t>21/07/1961</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12119,14 +12119,14 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>marek.krol82@wp.pl</t>
+          <t>marek.krol82@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>98040817908</t>
+          <t>62082817901</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1998-04-08</t>
+          <t>1962/28/08</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12206,14 +12206,14 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>barbara.wieczorek@onet.pl</t>
+          <t>barbara.wieczorek@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>91072419294</t>
+          <t>63090719296</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1991-07-24</t>
+          <t>07-09-1963</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12293,14 +12293,14 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>r.jablonski@xxx.uu</t>
+          <t>r.jablonski@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>79123020646</t>
+          <t>64101420640</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1979-12-30</t>
+          <t>1964-14-10</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>VQM749223</t>
+          <t>VQM849223</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -12380,14 +12380,14 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>witkowska.anna@yahoo.com</t>
+          <t>witkowska.anna@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>93072522031</t>
+          <t>65112122037</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1993-07-25</t>
+          <t>19651121</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -12467,14 +12467,14 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>tomaszwalczak@proton.me</t>
+          <t>tomaszwalczak@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>73042123385</t>
+          <t>66122823387</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1973-04-21</t>
+          <t>28/12/1966</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t/>
+          <t>BAI102309</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -12554,14 +12554,14 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>katarzyna_stepien@o2.pl</t>
+          <t>katarzyna_stepien@proton.me</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>97022524777</t>
+          <t>67010724775</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>1997-02-25</t>
+          <t>1967/07/01</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -12641,14 +12641,14 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>krzysztof.baran88@icloud.com</t>
+          <t>krzysztof.baran88@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>77010826124</t>
+          <t>68021426124</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1977-01-08</t>
+          <t>14-02-1968</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -12735,7 +12735,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>97013027513</t>
+          <t>69032127510</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1997-01-30</t>
+          <t>1969-21-03</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t/>
+          <t>PA5532920</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>+48 525 273 611</t>
+          <t>+48 502 275 283</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -12822,7 +12822,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>68110428860</t>
+          <t>70042828869</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>1968-11-04</t>
+          <t>19700428</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>PL1009677</t>
+          <t/>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>+48 555 187 775</t>
+          <t>788693410</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>68060930251</t>
+          <t>71050730256</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>1968-06-09</t>
+          <t>07/05/1971</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -12979,12 +12979,12 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>PL3212271</t>
+          <t/>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>556 486 342</t>
+          <t>+48 525 273 611</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -12996,7 +12996,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>00251331605</t>
+          <t>72061431604</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2000-05-13</t>
+          <t>1972/14/06</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13066,12 +13066,12 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>PA1105125</t>
+          <t>PL1009677</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>(48) 678881775</t>
+          <t>+48 555 187 775</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -13083,7 +13083,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>88011532998</t>
+          <t>73072132991</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>1988-01-15</t>
+          <t>21-07-1973</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13153,24 +13153,24 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t/>
+          <t>PL3212271</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>(48) 766343541</t>
+          <t>556 486 342</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>rafal.zajac94@bbb.ii</t>
+          <t>rafal.zajac94@abxza.pl</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>67091134346</t>
+          <t>74082834341</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1967-09-11</t>
+          <t>1974-28-08</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t/>
+          <t>PL</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t/>
+          <t>PA1105125</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>+48 717 324 164</t>
+          <t/>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -13257,7 +13257,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>90011435737</t>
+          <t>75090735734</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13277,12 +13277,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t/>
+          <t>Kowalski-Szymański</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1990-01-14</t>
+          <t>19750907</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13332,19 +13332,19 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>685 596 818</t>
+          <t>(48) 766343541</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>t.wojcicki@o2.pl</t>
+          <t>t.wojcicki@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>95101737089</t>
+          <t>76101437087</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>1995-10-17</t>
+          <t>14/10/1976</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t/>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -13419,19 +13419,19 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>(48) 654607799</t>
+          <t>+48 717 324 164</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>czarnecka.katarzyna.gmail.com@icloud.com</t>
+          <t>czarnecka.katarzyna@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>90080838477</t>
+          <t>77112138473</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>1990-08-08</t>
+          <t>1977/21/11</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13506,19 +13506,19 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>575901110</t>
+          <t>685 596 818</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>krzysztoflis@gmail.com</t>
+          <t>krzysztoflis@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>69030139821</t>
+          <t>78122839822</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>1969-03-01</t>
+          <t>28-12-1978</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13593,19 +13593,19 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>+48 609 797 136</t>
+          <t>(48) 654607799</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ewa_kolodziej@outlook.com</t>
+          <t>ewa_kolodziej@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>03280641215</t>
+          <t>79010741214</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2003-08-06</t>
+          <t>1979-07-01</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13675,24 +13675,24 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>P4689255</t>
+          <t/>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>+48 511 846 552</t>
+          <t>575901110</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>adam.kaczmarek71@wp.pl</t>
+          <t>adam.kaczmarek71@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>96112742565</t>
+          <t>80021442562</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1996-11-27</t>
+          <t>19800214</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13767,19 +13767,19 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>567 132 839</t>
+          <t>+48 609 797 136</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>monika.piatek@onet.pl</t>
+          <t>monika.piatek@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>69041643953</t>
+          <t>81032143958</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sadowsik</t>
+          <t>Sadwoski</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1969-04-16</t>
+          <t>21/03/1981</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Wrocł</t>
+          <t>Katowcie</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -13849,24 +13849,24 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t/>
+          <t>P4689255</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>548 316 005</t>
+          <t>+48 511 846 552</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>m.sadowski@interia.pl</t>
+          <t>m.sadowski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>88041045305</t>
+          <t>82042845308</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1988-04-10</t>
+          <t>1982/28/04</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -13936,24 +13936,24 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>PL1998522</t>
+          <t/>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>(48) 585250137</t>
+          <t>567 132 839</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>wlodarczyk.barbara@yahoo.com</t>
+          <t>wlodarczyk.barbara@proton.me</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>12281646694</t>
+          <t>93050746692</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2002-08-16</t>
+          <t>07-05-1983</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Wrocł</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14028,19 +14028,19 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>+48 622 776 443</t>
+          <t>548 316 005</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>rafalborkowski@uuu.ii</t>
+          <t>rafalborkowski@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>02320348044</t>
+          <t>84061448041</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14055,17 +14055,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2002-12-03</t>
+          <t>1984-14-06</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -14110,24 +14110,24 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>P6249254</t>
+          <t>PL1998522</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>(48) 709659943</t>
+          <t>(48) 585250137</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>anna_kowalska@o2.pl</t>
+          <t>anna_kowalska.krawczyk@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>72051849435</t>
+          <t>85072149437</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>1972-05-18</t>
+          <t>19850721</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14202,19 +14202,19 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>662247969</t>
+          <t>+48 622 776 443</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>tomasz.nowacki77@icloud.com</t>
+          <t>tomasz.nowacki77@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>80081150780</t>
+          <t>86082850780</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1980-08-11</t>
+          <t>28/08/1986</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14284,24 +14284,24 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>PA2358519</t>
+          <t>P6249254</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>694 215 605</t>
+          <t>(48) 709659943</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>katarzyna.wisniewska.gmail.com@gmail.com</t>
+          <t>katarzyna.wisniewska@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>99071652177</t>
+          <t>87090752174</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1999-07-16</t>
+          <t>07/09/1987 08:14</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -14376,19 +14376,19 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>48-654-824-720</t>
+          <t>662247969</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>k.wojcik@outlook.com</t>
+          <t>k.wojcik@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>79111353527</t>
+          <t>88101453525</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1979-11-13</t>
+          <t>14-10-1988</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Toruń</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14458,24 +14458,24 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>P3502610</t>
+          <t>PA2358519</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>48-723-780-633</t>
+          <t>694 215 605</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>kowalczyk.ewa@wp.pl</t>
+          <t>kowalczyk.ewa@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>88062054919</t>
+          <t>89112154911</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1988-06-20</t>
+          <t>1989-21-11</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -14550,19 +14550,19 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>570 500 727</t>
+          <t>48-654-824-720</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>adamkaminski@onet.pl</t>
+          <t>adamkaminski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>67070156268</t>
+          <t>90122856261</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1967-07-01</t>
+          <t>19901228</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14632,24 +14632,24 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t/>
+          <t>P3502610</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>(48) 593263908</t>
+          <t>48-723-780-633</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>monika_lewandowska@interia.pl</t>
+          <t>monika_lewandowska@proton.me</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>95061457650</t>
+          <t>91010757659</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1995-06-14</t>
+          <t>07/01/1991</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14719,12 +14719,12 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>P9764778</t>
+          <t/>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>719723089</t>
+          <t>570 500 727</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
@@ -14736,7 +14736,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>82071759005</t>
+          <t>92021459008</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1982-07-17</t>
+          <t>1992/14/02</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -14811,19 +14811,19 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>653243630</t>
+          <t>(48) 593263908</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>barbara.szymanska@proton.me</t>
+          <t>barbara.szymanska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>82062260392</t>
+          <t>93032160398</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1982-06-22</t>
+          <t>21-03-1993</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -14893,24 +14893,24 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>PL3800572</t>
+          <t>P9764778</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>(48) 587229662</t>
+          <t>719723089</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>r.dabrowski@qqq.zz</t>
+          <t>r.dabrowski@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>91060661746</t>
+          <t>94042861747</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1991-06-06</t>
+          <t>1994-28-04</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -14980,24 +14980,24 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>PL2492440</t>
+          <t/>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>728216354</t>
+          <t>653243630</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>mazur.anna@icloud.com</t>
+          <t>mazur.anna@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>96121163135</t>
+          <t>95050763131</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1996-12-11</t>
+          <t>19950507</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15067,24 +15067,24 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>PA6319951</t>
+          <t>PL3800572</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>656 582 113</t>
+          <t>(48) 587229662</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>tomaszkrawczyk@gmail.com</t>
+          <t>tomaszkrawczyk@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>68102464483</t>
+          <t>96061464480</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>1968-10-24</t>
+          <t>14/06/1996</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15154,24 +15154,24 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2492440</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>730166519</t>
+          <t>728216354</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>katarzyna_wozniak.gmail.com@outlook.com</t>
+          <t>katarzyna_wozniak@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>92081565871</t>
+          <t>97072165876</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>1992-08-15</t>
+          <t>1997/21/07</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -15241,24 +15241,24 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t/>
+          <t>PA6319951</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>(48) 502462281</t>
+          <t>656 582 113</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>krzysztof.jankowski89@wp.pl</t>
+          <t>krzysztof.jankowski89@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>02310267225</t>
+          <t>98082867226</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2002-11-02</t>
+          <t>28-08-1998</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15333,19 +15333,19 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>746 391 410</t>
+          <t>730166519</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>ewa.grabowska@onet.pl</t>
+          <t>ewa.grabowska@proton.me</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>91081268616</t>
+          <t>99090768619</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>1991-08-12</t>
+          <t>1999-07-09</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -15420,19 +15420,19 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>707857404</t>
+          <t>(48) 502462281</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>a.pawlak@interia.pl</t>
+          <t>a.pawlak@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>91060769963</t>
+          <t>00301469966</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>1991-06-07</t>
+          <t>20001014</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -15507,19 +15507,19 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>(48) 778728075</t>
+          <t>746 391 410</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>michalska.monika@yahoo.com</t>
+          <t>michalska.monika@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>04221971352</t>
+          <t>01312171356</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2004-02-19</t>
+          <t>21/11/2001</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -15589,24 +15589,24 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>PA2277949</t>
+          <t/>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>618 880 851</t>
+          <t>707857404</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>marekkrol@proton.me</t>
+          <t>marekkrol@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>82080272704</t>
+          <t>02322872705</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>1982-08-02</t>
+          <t>2002/28/12</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -15681,19 +15681,19 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>+48 772 798 758</t>
+          <t>(48) 778728075</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>barbara_wieczorek@o2.pl</t>
+          <t>barbara_wieczorek@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>71041174098</t>
+          <t>03210774095</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1971-04-11</t>
+          <t>07-01-2003</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -15763,24 +15763,24 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>PL5957709</t>
+          <t>PA2277949</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>(48) 704370174</t>
+          <t>618 880 851</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>rafal.jablonski95@abc.yy</t>
+          <t>rafal.jablonski95@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>76112075447</t>
+          <t>04221475443</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>1976-11-20</t>
+          <t>2004-14-02</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -15850,24 +15850,24 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>PA6817685</t>
+          <t/>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>+48 562 893 965</t>
+          <t>+48 772 798 758</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>anna.witkowska@gmail.com</t>
+          <t>anna.witkowska@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>83021076834</t>
+          <t>05232176839</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>1983-02-10</t>
+          <t>20050321</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -15937,24 +15937,24 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t/>
+          <t>PL5957709</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>532 165 021</t>
+          <t>(48) 704370174</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>t.walczak@outlook.com</t>
+          <t>t.walczak@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>79061278189</t>
+          <t>60042878186</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1979-06-12</t>
+          <t>28/04/1960</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -16024,24 +16024,24 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>PA2799307</t>
+          <t>PA6817685</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>+48 746 837 914</t>
+          <t>+48 562 893 965</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>stepien.katarzyna.gmail.com@wp.pl</t>
+          <t>stepien.katarzyna@proton.me</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>82021279575</t>
+          <t>61050779579</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>1982-02-12</t>
+          <t>1961/07/05</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -16116,19 +16116,19 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>+48 769 756 308</t>
+          <t>532 165 021</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>krzysztofbaran@onet.pl</t>
+          <t>krzysztofbaran@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>92030280921</t>
+          <t>62061480920</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1992-03-02</t>
+          <t>14-06-1962</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -16198,24 +16198,24 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2799307</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>+48 625 682 313</t>
+          <t>+48 746 837 914</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>ewa_rutkowska@interia.pl</t>
+          <t>ewa_rutkowska@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>94070982319</t>
+          <t>63072182317</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1994-07-09</t>
+          <t>1963-21-07</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -16250,7 +16250,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -16285,24 +16285,24 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>PL6396582</t>
+          <t/>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>571 926 000</t>
+          <t>+48 769 756 308</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>adam.gorski72@yahoo.com</t>
+          <t>adam.gorski72@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>75092383669</t>
+          <t>64082883667</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16327,7 +16327,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>1975-09-23</t>
+          <t>19640828</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -16377,19 +16377,19 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>751 190 376</t>
+          <t>+48 625 682 313</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>monika.sikora@proton.me</t>
+          <t>monika.sikora@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>00262585059</t>
+          <t>65090785051</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2000-06-25</t>
+          <t>07/09/1965</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -16459,24 +16459,24 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>PA5401604</t>
+          <t>PL6396582</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>48-700-875-199</t>
+          <t>571 926 000</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>m.ostrowski@o2.pl</t>
+          <t>m.ostrowski@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>91041286401</t>
+          <t>66101486402</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>1991-04-12</t>
+          <t>1966/14/10</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -16551,19 +16551,19 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>592 820 349</t>
+          <t>751 190 376</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>tomaszewska.barbara@icloud.com</t>
+          <t>tomaszewska.barbara@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>95112787794</t>
+          <t>67112187799</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>1995-11-27</t>
+          <t>21-11-1967</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -16633,24 +16633,24 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t/>
+          <t>PA5401604</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>48-595-228-644</t>
+          <t>48-700-875-199</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>rafalzajac@xxx.uu</t>
+          <t>rafalzajac@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>84091689140</t>
+          <t>68122889149</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>1984-09-16</t>
+          <t>1968-28-12</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -16725,19 +16725,19 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>591 258 662</t>
+          <t>592 820 349</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>anna_pietrzak@outlook.com</t>
+          <t>anna_pietrzak@proton.me</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>91050890532</t>
+          <t>69010790530</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1991-05-08</t>
+          <t>19690107</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -16807,24 +16807,24 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>PA3523980</t>
+          <t/>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>48-655-961-184</t>
+          <t>48-595-228-644</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>tomasz.wojcicki78@wp.pl</t>
+          <t>tomasz.wojcicki78@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>70092691888</t>
+          <t>70021491888</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1970-09-26</t>
+          <t>14/02/1970</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -16899,19 +16899,19 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>(48) 675375387</t>
+          <t>591 258 662</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>katarzyna.czarnecka.gmail.com@onet.pl</t>
+          <t>katarzyna.czarnecka@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>81012993278</t>
+          <t>71032193275</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>1981-01-29</t>
+          <t>1971/21/03</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -16946,7 +16946,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -16981,24 +16981,24 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>PA9658376</t>
+          <t>PA3523980</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>+48 690 409 695</t>
+          <t>48-655-961-184</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>k.lis@interia.pl</t>
+          <t>k.lis@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>85042594623</t>
+          <t>72042894624</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>1985-04-25</t>
+          <t>28-04-1972</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -17068,24 +17068,24 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>PA3447977</t>
+          <t/>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>774 434 477</t>
+          <t>(48) 675375387</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>kolodziej.ewa@yahoo.com</t>
+          <t>kolodziej.ewa@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>84073096014</t>
+          <t>73050796018</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>1984-07-30</t>
+          <t>1973-07-05</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -17155,24 +17155,24 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t/>
+          <t>PA9658376</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>(48) 656868868</t>
+          <t>+48 690 409 695</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>adamkaczmarek@proton.me</t>
+          <t>adamkaczmarek@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>84112697367</t>
+          <t>74061497367</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>1984-11-26</t>
+          <t>19740614</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -17237,29 +17237,29 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>HKE935631</t>
+          <t>HKE035631</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t/>
+          <t>PA3447977</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>(48) 708349558</t>
+          <t>774 434 477</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>monika_piatek@o2.pl</t>
+          <t>monika_piatek@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>90042198753</t>
+          <t>75072198753</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>1990-04-21</t>
+          <t>21/07/1975</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>pOole</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -17329,24 +17329,24 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>PA7053075</t>
+          <t/>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>(48) 758455703</t>
+          <t>(48) 656868868</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>marek.sadowski84@icloud.com</t>
+          <t>marek.sadowski84@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>87110100101</t>
+          <t>76082800106</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>1987-11-01</t>
+          <t>1976/28/08</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -17421,19 +17421,19 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>48-545-880-496</t>
+          <t>(48) 708349558</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>barbara.wlodarczyk@gmail.com</t>
+          <t>barbara.wlodarczyk@proton.me</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>75100901494</t>
+          <t>77090701490</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>1975-10-09</t>
+          <t>07-09-1977</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>pOole</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>PL2890785</t>
+          <t>PA7053075</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>539 887 629</t>
+          <t>(48) 758455703</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>r.borkowski@bbb.ii</t>
+          <t>r.borkowski@uuu.xs</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/pesel.xlsx
+++ b/data/xlsx/pesel.xlsx
@@ -155,7 +155,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -165,12 +165,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -190,7 +190,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PL4755810</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -252,12 +252,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -277,7 +277,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t/>
+          <t>PA0300378</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -329,7 +329,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -339,12 +339,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -364,7 +364,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>PB0303949</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -416,7 +416,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t/>
+          <t>PC0307520</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PL1213488</t>
+          <t>PL0311091</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>P3474580</t>
+          <t/>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t/>
+          <t>PA0318233</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mraek</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Mcihał</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>pOol</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t/>
+          <t>PB0321804</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>P3404168</t>
+          <t>PC0325375</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>79112119190</t>
+          <t>69112119190</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PA4390829</t>
+          <t>PL0328946</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t/>
+          <t>PA0336088</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>P8508672</t>
+          <t>PB0339659</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Krakow</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t/>
+          <t>PC0343230</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t/>
+          <t>PL0346801</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PA4781605</t>
+          <t>PA0353943</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>PL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t/>
+          <t>PB0357514</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1731,12 +1731,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t/>
+          <t>PC0361085</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PA2616842</t>
+          <t>PL0364656</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t/>
+          <t>PA0371798</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Toruń</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>P1491097</t>
+          <t>PB0375369</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Toruń</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t/>
+          <t>PC0378940</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t/>
+          <t>PL0382511</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>PA9556848</t>
+          <t>PA0389653</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PA3592018</t>
+          <t>PB0393224</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>RSG250607</t>
+          <t>RSG150607</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t/>
+          <t>PC0396795</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t/>
+          <t>PL0400366</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Pruszków</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Piaseczno</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>PA4853513</t>
+          <t>PA2550108</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Wieliczka</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2553679</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Oświęcim</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2557250</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Krosno</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2560821</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Mielec</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Świdnica</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2567963</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Kłodzko</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2571534</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Gniezno</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2575105</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Leszno</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2578676</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Tczew</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Wejherowo</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>PA8175810</t>
+          <t>PA2585818</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Cieszyn</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2589389</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Będzin</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>PL4534077</t>
+          <t>PC2592960</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Inowrocław</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2596531</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Grudziądz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Ostróda</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>P5900479</t>
+          <t>PA2603673</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Giżycko</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>P4928483</t>
+          <t>PB2607244</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Puławy</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2610815</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Zamość</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2614386</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Augustów</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Suwałki</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>P9695950</t>
+          <t>PA2621528</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Nysa</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>PL8874187</t>
+          <t>PB2625099</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Wrocłah</t>
+          <t>Brzeg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2628670</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Żary</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t/>
+          <t>PL3632241</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Świebodzin</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Kołobrzeg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2639383</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Marke</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ieKlec</t>
+          <t>Stargard</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>PL6799346</t>
+          <t>PB2642954</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Sandomierz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>P3943843</t>
+          <t>PC2646525</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5253,7 +5253,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>85010709694</t>
+          <t>75010709694</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>P3191160</t>
+          <t>PL2650096</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>PL9406100</t>
+          <t>PA2657238</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>PA9652310</t>
+          <t>PB2660809</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>P9758448</t>
+          <t>PC2664380</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5733,12 +5733,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>PA2845185</t>
+          <t>PL2667951</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Poznfń</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2675093</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2678664</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>P6662066</t>
+          <t>PC2682235</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2685806</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>PA7806091</t>
+          <t/>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2692948</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2696519</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>PL7651435</t>
+          <t>PC2700090</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2703661</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2710803</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2714374</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2717945</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2721516</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>PA5391057</t>
+          <t/>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2728658</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Toruń</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t/>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>PA6720688</t>
+          <t>PB2732229</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t/>
+          <t>+48 510 692 520</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Toruń</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2735800</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>JWU862815</t>
+          <t>JWU762815</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2739371</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2746513</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7689,7 +7689,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>03250748056</t>
+          <t>13250748056</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>PL8443206</t>
+          <t>PB2750084</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2753655</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2757226</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>P5337594</t>
+          <t>PB2767939</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2771510</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2775081</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Pruszków</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>PA8660726</t>
+          <t>PA2782223</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Piaseczno</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2785794</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Wieliczka</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2789365</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Oświęcim</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2792936</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Krosno</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8865,12 +8865,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>P7021186</t>
+          <t/>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Mielec</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>PA9578808</t>
+          <t>PA2800078</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Świdnica</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2803649</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Kłodzko</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2807220</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Gniezno</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2810791</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Leszno</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>PL8809488</t>
+          <t/>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Tczew</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2817933</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Mcihał</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Szcz</t>
+          <t>Wejherowo</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2821504</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Cieszyn</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2825075</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>89032178195</t>
+          <t>79032178195</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Będzin</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>PA2983884</t>
+          <t>PL2828646</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Inowrocław</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Grudziądz</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2835788</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Ostróda</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -9909,12 +9909,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2839359</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Giżycko</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>PL9092973</t>
+          <t>PC2842930</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Puławy</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2846501</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Zamość</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>P3601348</t>
+          <t/>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Augustów</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2853643</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bydgoszz</t>
+          <t>Suwałki</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -10344,12 +10344,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>PL1247498</t>
+          <t>PB2857214</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Nysa</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2860785</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Brzeg</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>P1095916</t>
+          <t>PL2864356</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Żary</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10605,12 +10605,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Świebodzin</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>PA1770285</t>
+          <t>PA2871498</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Kołobrzeg</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>PL2921112</t>
+          <t>PB2875069</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Stargard</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2878640</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Sandomierz</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -10953,12 +10953,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2882211</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>P9562455</t>
+          <t>PA2889353</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2892924</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -11301,12 +11301,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>PL1353650</t>
+          <t>PC2896495</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>PL6688025</t>
+          <t>PL2900066</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>PA9060697</t>
+          <t/>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2907208</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2910779</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2914350</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2917921</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Poznań</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -11910,12 +11910,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -11997,12 +11997,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>PL3931143</t>
+          <t>PA2925063</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2928634</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Zielona Góra</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12171,12 +12171,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2932205</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12258,12 +12258,12 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2935776</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12345,12 +12345,12 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>VQM849223</t>
+          <t>VQM749223</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>PA2151995</t>
+          <t/>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Katowice</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>PA6946529</t>
+          <t>PA2942918</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12519,12 +12519,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2946489</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>PA5532920</t>
+          <t>PC2950060</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2953631</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>PA5532920</t>
+          <t/>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2960773</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2964344</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Toruń</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>PL1009677</t>
+          <t>PC2967915</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Toruń</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>PL3212271</t>
+          <t>PL2971486</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13215,12 +13215,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>PA1105125</t>
+          <t/>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Rzeszów</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2978628</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -13379,22 +13379,22 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t/>
+          <t>PL</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t/>
+          <t>PB2982199</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13476,12 +13476,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t/>
+          <t>PC2985770</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t/>
+          <t>PL2989341</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t/>
+          <t>PA2996483</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sadwoski</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Katowcie</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -13824,12 +13824,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>P4689255</t>
+          <t>PB3000054</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -13911,12 +13911,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t/>
+          <t>PC3003625</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -13953,7 +13953,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>93050746692</t>
+          <t>83050746692</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Wrocł</t>
+          <t>Zielona Góra</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t/>
+          <t>PL3007196</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14085,12 +14085,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>PL1998522</t>
+          <t/>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Gdynia</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t/>
+          <t>PA3014338</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Pruszków</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>P6249254</t>
+          <t>PB3017909</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Piaseczno</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -14346,12 +14346,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t/>
+          <t>PC3021480</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Wieliczka</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14433,12 +14433,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>PA2358519</t>
+          <t>PL3025051</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Oświęcim</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Krosno</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>P3502610</t>
+          <t>PA3032193</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Mielec</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14694,12 +14694,12 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t/>
+          <t>PB3035764</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Świdnica</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -14781,12 +14781,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t/>
+          <t>PC3039335</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Kłodzko</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -14868,12 +14868,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>P9764778</t>
+          <t>PL3042906</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Gniezno</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -14955,12 +14955,12 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Leszno</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>PL3800572</t>
+          <t>PA3050048</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Tczew</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>PL2492440</t>
+          <t>PB3053619</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Wejherowo</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -15216,12 +15216,12 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>PA6319951</t>
+          <t>PC3057190</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Cieszyn</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15303,12 +15303,12 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t/>
+          <t>PL3060761</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Będzin</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -15390,12 +15390,12 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Inowrocław</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -15477,12 +15477,12 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t/>
+          <t>PA3067903</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Grudziądz</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t/>
+          <t>PB3071474</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Ostróda</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -15651,12 +15651,12 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t/>
+          <t>PC3075045</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Giżycko</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -15738,12 +15738,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>PA2277949</t>
+          <t>PL3078616</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Puławy</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -15825,12 +15825,12 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Zamość</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -15912,12 +15912,12 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>PL5957709</t>
+          <t>PA3085758</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Augustów</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -15999,12 +15999,12 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>PA6817685</t>
+          <t>PB3089329</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Suwałki</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -16086,12 +16086,12 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t/>
+          <t>PC3092900</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Nysa</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>PA2799307</t>
+          <t>PL3096471</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -16250,7 +16250,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Brzeg</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Żary</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -16347,12 +16347,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t/>
+          <t>PA3103613</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Świebodzin</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>PL6396582</t>
+          <t>PB3107184</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Kołobrzeg</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -16521,12 +16521,12 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t/>
+          <t>PC3110755</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Stargard</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -16608,12 +16608,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>PA5401604</t>
+          <t>PL3114326</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Sandomierz</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -16695,12 +16695,12 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -16782,12 +16782,12 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t/>
+          <t>PA3121468</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -16869,12 +16869,12 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Wojciech</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Agnieszka</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t/>
+          <t>PB3125039</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -16946,7 +16946,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -16956,12 +16956,12 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>PA3523980</t>
+          <t>PC3128610</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -17043,12 +17043,12 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t/>
+          <t>PL3132181</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -17130,12 +17130,12 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>PA9658376</t>
+          <t/>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -17217,12 +17217,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -17237,12 +17237,12 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>HKE035631</t>
+          <t>HKE935631</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>PA3447977</t>
+          <t>PA3139323</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -17304,12 +17304,12 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t/>
+          <t>PB3142894</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -17391,12 +17391,12 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Paweł</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t/>
+          <t>PC3146465</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>pOole</t>
+          <t>Wrocław</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -17478,12 +17478,12 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>PA7053075</t>
+          <t>PL3150036</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">

--- a/data/xlsx/pesel.xlsx
+++ b/data/xlsx/pesel.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>60021406849</t>
+          <t>62021428841</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -135,17 +135,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1960-14-02</t>
+          <t>1962-14-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -155,7 +155,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Gliwice</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -170,17 +170,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
+          <t>ul. Zwycięstwa 121/61, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
+          <t>ul. Zwycięstwa 121/61, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -200,14 +200,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>anna.kowalska.krawczyk@gmail.com</t>
+          <t>anna.lewandowska.krol@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61032108236</t>
+          <t>63032130231</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -222,7 +222,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -232,7 +232,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19610321</t>
+          <t>19630321</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Warszawa</t>
+          <t>Tychy</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -252,32 +252,32 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Cezary</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Weronika</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
+          <t>ul Bocheńskiego 138, 43-100 Tychy</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
+          <t>ul Bocheńskiego 138, 43-100 Tychy</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ONV883946</t>
+          <t>UXR609746</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PA0300378</t>
+          <t>PA2442978</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -287,14 +287,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>t.nowacki@outlook.com</t>
+          <t>t.zielinski@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62042809586</t>
+          <t>64042831581</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -309,17 +309,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28/04/1962</t>
+          <t>28/04/1964</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -329,7 +329,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Częstochowa</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -339,32 +339,32 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Norbert</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Wiktoria</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ulica Floriańska 35, 31-019 Kraków</t>
+          <t>ulica Najświętszej Maryi Panny 155, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ulica Floriańska 35, 31-019 Kraków</t>
+          <t>ulica Najświętszej Maryi Panny 155, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>RSG860489</t>
+          <t>XCC886289</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PB0303949</t>
+          <t>PB2446549</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -374,14 +374,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>wisniewska.katarzyna@wp.pl</t>
+          <t>szymanska.katarzyna@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>63050710972</t>
+          <t>65050732974</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -396,7 +396,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -406,7 +406,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1963/07/05</t>
+          <t>1965/07/05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -416,7 +416,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kraków</t>
+          <t>Bielsko-Biała</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -426,32 +426,32 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Zofia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Długa 52, 31-147 Kraków</t>
+          <t>11 Listopada 172, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Długa 52, 31-147 Kraków</t>
+          <t>11 Listopada 172, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>UXR537032</t>
+          <t>AHN762832</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PC0307520</t>
+          <t>PC2450120</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -461,14 +461,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>krzysztofwojcik@onet.pl</t>
+          <t>krzysztofdabrowski@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>64061412321</t>
+          <t>66061434323</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -483,17 +483,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Jabłońska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-06-1964</t>
+          <t>14-06-1966</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Niechobrz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -513,32 +513,32 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kacper</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
+          <t>9/23, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
+          <t>9/23, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>XCC413575</t>
+          <t>DMY639375</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PL0311091</t>
+          <t>PL2453691</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -548,14 +548,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ewa_kowalczyk@interia.pl</t>
+          <t>ewa_mazur@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>65072113717</t>
+          <t>67072135719</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1965-21-07</t>
+          <t>1967-21-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Łódź</t>
+          <t>Przemyśl</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -600,27 +600,27 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Mikołaj</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ul Zachodnia 86, 90-402 Łódź</t>
+          <t>ul Franciszkańska 26, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ul Zachodnia 86, 90-402 Łódź</t>
+          <t>ul Franciszkańska 26, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>AHN990118</t>
+          <t>GRJ415918</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -635,14 +635,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>adam.kaminski75@o2.pl</t>
+          <t>adam.krawczyk95@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>66082815068</t>
+          <t>68082837060</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19660828</t>
+          <t>19680828</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Sanok</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Szymon</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Kinga</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
+          <t>ulica Kościuszki 43, 38-500 Sanok</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
+          <t>ulica Kościuszki 43, 38-500 Sanok</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>DMY266661</t>
+          <t>JWU792461</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PA0318233</t>
+          <t>PA2460833</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -722,14 +722,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>monika.lewandowska@proton.me</t>
+          <t>monika.wozniak@proton.me</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>67090716451</t>
+          <t>69090738453</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/09/1967</t>
+          <t>07/09/1969</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Wrocław</t>
+          <t>Białystok</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -774,32 +774,32 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Antoni</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Legnicka 120, 54-203 Wrocław</t>
+          <t>Suraska 60, 15-422 Białystok</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Legnicka 120, 54-203 Wrocław</t>
+          <t>Suraska 60, 15-422 Białystok</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GRJ343204</t>
+          <t>MBF369004</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PB0321804</t>
+          <t>PB2464404</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>m.zielinski@yahoo.com</t>
+          <t>m.jankowski@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>68101417802</t>
+          <t>70101439803</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1968/14/10</t>
+          <t>1970/14/10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Ogrodniczki</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Aleksander</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Kamila</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
+          <t>77/75, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
+          <t>77/75, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PC0325375</t>
+          <t>PC2467975</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -896,14 +896,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>szymanska.barbara@gmail.com</t>
+          <t>grabowska.barbara@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>69112119190</t>
+          <t>71112141194</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21-11-1969</t>
+          <t>21-11-1971</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Poznań</t>
+          <t>Hajnówka</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -948,32 +948,32 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Franciszek</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Sylwia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ul Głogowska 154, 60-734 Poznań</t>
+          <t>os. 3 Maja 94, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ul Głogowska 154, 60-734 Poznań</t>
+          <t>os. 3 Maja 94, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MBF896290</t>
+          <t>SLB322090</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PL0328946</t>
+          <t>PL2471546</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -983,14 +983,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>rafaldabrowski@outlook.com</t>
+          <t>rafalpawlak@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>70122820541</t>
+          <t>72122842543</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Górska</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1970-28-12</t>
+          <t>1972-28-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Lublin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1035,27 +1035,27 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Ignacy</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Halina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ulica Długa 171, 80-831 Gdańsk</t>
+          <t>ulica os. LSM 111, 20-400 Lublin</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ulica Długa 171, 80-831 Gdańsk</t>
+          <t>ulica os. LSM 111, 20-400 Lublin</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>PGQ272833</t>
+          <t>VQM098633</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1070,14 +1070,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>aleksandra_mazur@wp.pl</t>
+          <t>aleksandra_michalska@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>71010721939</t>
+          <t>73010743931</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19710107</t>
+          <t>19730107</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Gdańsk</t>
+          <t>Mięćmierz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1122,32 +1122,32 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nikodem</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Grażyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
+          <t>128, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
+          <t>128, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SLB549376</t>
+          <t>YVX675176</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PA0336088</t>
+          <t>PA2478688</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1157,14 +1157,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>andrzej.krawczyk81@onet.pl</t>
+          <t>andrzej.krol72@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>72021423289</t>
+          <t>74021445281</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14/02/1972</t>
+          <t>14/02/1974</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Biała Podlaska</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1209,32 +1209,32 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Danuta</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
+          <t>ul. Brzeska 145/37, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
+          <t>ul. Brzeska 145/37, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>VQM925919</t>
+          <t>BAI451719</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PB0339659</t>
+          <t>PB2482259</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1244,14 +1244,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>marta.wozniak@interia.pl</t>
+          <t>marta.wieczorek@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>73032124675</t>
+          <t>75032146677</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1973/21/03</t>
+          <t>1975/21/03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Szczecin</t>
+          <t>Toruń</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1296,32 +1296,32 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Miłosz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Bożena</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
+          <t>ul Rynek Staromiejski 162, 87-100 Toruń</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
+          <t>ul Rynek Staromiejski 162, 87-100 Toruń</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>YVX202462</t>
+          <t>EFT028262</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PC0343230</t>
+          <t>PC2485830</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>l.jankowski@o2.pl</t>
+          <t>l.jablonski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>74042826025</t>
+          <t>76042848027</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28-04-1974</t>
+          <t>28-04-1976</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Bydgoszcz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1383,32 +1383,32 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Aneta</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ulica Mariacka 59, 40-014 Katowice</t>
+          <t>ulica Mostowa 179, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ulica Mariacka 59, 40-014 Katowice</t>
+          <t>ulica Mostowa 179, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BAI679005</t>
+          <t>HKE804805</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PL0346801</t>
+          <t>PL2489401</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>grabowska.paulina@proton.me</t>
+          <t>witkowska.paulina@proton.me</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>75050727418</t>
+          <t>77050749410</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1975-07-05</t>
+          <t>1977-07-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Olsztyn</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1470,27 +1470,27 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Tadeusz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Zuzanna</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Warszawska 76, 40-009 Katowice</t>
+          <t>Stare Miasto 16, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Warszawska 76, 40-009 Katowice</t>
+          <t>Stare Miasto 16, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>EFT955548</t>
+          <t>KPP481348</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1505,14 +1505,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>mateuszpawlak@yahoo.com</t>
+          <t>mateuszwalczak@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>76061428767</t>
+          <t>78061450762</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Wójcicka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19760614</t>
+          <t>19780614</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Mrągowo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Jerzy</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Maja</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
+          <t>ul. Warszawska 33/89, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
+          <t>ul. Warszawska 33/89, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PA0353943</t>
+          <t>PA2496543</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1592,14 +1592,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>elzbieta_michalska@gmail.com</t>
+          <t>elzbieta_stepien@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>77072130157</t>
+          <t>79072152159</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21/07/1977</t>
+          <t>21/07/1979</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lublin</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1644,32 +1644,32 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ul Narutowicza 110, 20-004 Lublin</t>
+          <t>ul Wojska Polskiego 50, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ul Narutowicza 110, 20-004 Lublin</t>
+          <t>ul Wojska Polskiego 50, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>KPP308634</t>
+          <t>QZL834434</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PB0357514</t>
+          <t>PB2500114</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1679,14 +1679,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>dawid.krol87@outlook.com</t>
+          <t>dawid.baran78@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>78082831506</t>
+          <t>80082853507</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1978/28/08</t>
+          <t>1980/28/08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Świnoujście</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1731,32 +1731,32 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Marian</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Oliwia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ulica Lipowa 127, 15-424 Białystok</t>
+          <t>ulica Monte Cassino 67, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ulica Lipowa 127, 15-424 Białystok</t>
+          <t>ulica Monte Cassino 67, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>NUA385177</t>
+          <t>TEW310977</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PC0361085</t>
+          <t>PC2503685</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1766,14 +1766,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>dorota.wieczorek@wp.pl</t>
+          <t>dorota.rutkowska@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>79090732890</t>
+          <t>81090754891</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>07-09-1979</t>
+          <t>07-09-1981</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Józef</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>QZL461720</t>
+          <t>WJH487520</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PL0364656</t>
+          <t>PL2507256</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1853,14 +1853,14 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>d.jablonski@onet.pl</t>
+          <t>d.gorski@onet.pl</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>80101434241</t>
+          <t>82101456243</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1980-14-10</t>
+          <t>1982-14-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Kluczbork</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1910,22 +1910,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
+          <t>ul. Byczyńska 101/51, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
+          <t>ul. Byczyńska 101/51, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>TEW538263</t>
+          <t>ZOS064063</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1940,14 +1940,14 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>witkowska.beata@interia.pl</t>
+          <t>sikora.beata@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>81112135637</t>
+          <t>83112157639</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>19811121</t>
+          <t>19831121</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bydgoszcz</t>
+          <t>Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1992,32 +1992,32 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
+          <t>ul Chrobrego 118, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
+          <t>ul Chrobrego 118, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>WJH314806</t>
+          <t>CTD640606</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PA0371798</t>
+          <t>PA2514398</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2027,14 +2027,14 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>slawomirwalczak@o2.pl</t>
+          <t>slawomirostrowski@o2.pl</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>82122836987</t>
+          <t>84122858989</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2049,17 +2049,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Sadowska</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>28/12/1982</t>
+          <t>28/12/1984</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Międzyrzecz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2079,32 +2079,32 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Mirosław</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Gabriela</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ulica Szeroka 15, 87-100 Toruń</t>
+          <t>ulica 30 Stycznia 135, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>ulica Szeroka 15, 87-100 Toruń</t>
+          <t>ulica 30 Stycznia 135, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ZOS991349</t>
+          <t>FYO517149</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>PB0375369</t>
+          <t>PB2517969</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2114,14 +2114,14 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>urszula_stepien@proton.me</t>
+          <t>urszula_tomaszewska@proton.me</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>83010738376</t>
+          <t>85010760371</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1983/07/01</t>
+          <t>1985/07/01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Kielce</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2166,32 +2166,32 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Martyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Chełmińska 32, 87-100 Toruń</t>
+          <t>Paderewskiego 152, 25-004 Kielce</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Chełmińska 32, 87-100 Toruń</t>
+          <t>Paderewskiego 152, 25-004 Kielce</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>CTD467892</t>
+          <t>IDZ793692</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PC0378940</t>
+          <t>PC2521540</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2201,14 +2201,14 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>mariusz.baran93@yahoo.com</t>
+          <t>mariusz.zajac84@yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>84021439724</t>
+          <t>86021461729</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14-02-1984</t>
+          <t>14-02-1986</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Busko-Zdrój</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2253,22 +2253,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Dominika</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
+          <t>ul. 1 Maja 169/13, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
+          <t>ul. 1 Maja 169/13, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PL0382511</t>
+          <t>PL2525111</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2288,14 +2288,14 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>izabela.rutkowska@gmail.com</t>
+          <t>izabela.pietrzak@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>85032141114</t>
+          <t>87032163116</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1985-21-03</t>
+          <t>1987-21-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rzeszów</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2340,27 +2340,27 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
+          <t>ul Marszałkowska 6, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
+          <t>ul Marszałkowska 6, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>IDZ620978</t>
+          <t>ONV446778</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2375,14 +2375,14 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>h.gorski@outlook.com</t>
+          <t>h.wojcicki@outlook.com</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>86042842464</t>
+          <t>88042864466</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2397,17 +2397,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>19860428</t>
+          <t>19880428</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2427,32 +2427,32 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Jagoda</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
+          <t>ulica Krakowskie Przedmieście 23, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
+          <t>ulica Krakowskie Przedmieście 23, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>LIK797521</t>
+          <t>RSG223321</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>PA0389653</t>
+          <t>PA2532253</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>sikora.weronika@wp.pl</t>
+          <t>czarnecka.weronika@wp.pl</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>87050743857</t>
+          <t>89050765859</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>07/05/1987</t>
+          <t>07/05/1989</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kielce</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2514,32 +2514,32 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Warszawska 100, 25-512 Kielce</t>
+          <t>Floriańska 40, 31-019 Kraków</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Warszawska 100, 25-512 Kielce</t>
+          <t>Floriańska 40, 31-019 Kraków</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ONV374064</t>
+          <t>UXR899864</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PB0393224</t>
+          <t>PB2535824</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2549,14 +2549,14 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>stanislawostrowski@onet.pl</t>
+          <t>stanislawlis@onetpl</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>88061445206</t>
+          <t>90061467207</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Pawłowska</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1988/14/06</t>
+          <t>1990/14/06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2601,32 +2601,32 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Krystyna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
+          <t>ul. Długa 57/65, 31-147 Kraków</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
+          <t>ul. Długa 57/65, 31-147 Kraków</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>RSG150607</t>
+          <t>XCC176407</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>PC0396795</t>
+          <t>PC2539395</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>zofia_tomaszewska@interia.pl</t>
+          <t>zofia_kolodziej@interia.pl</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>89072146593</t>
+          <t>91072168594</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>21-07-1989</t>
+          <t>21-07-1991</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Olsztyn</t>
+          <t>Łódź</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2688,32 +2688,32 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Jadwiga</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
+          <t>ul Piotrkowska 74, 90-102 Łódź</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
+          <t>ul Piotrkowska 74, 90-102 Łódź</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>UXR727150</t>
+          <t>AHN952950</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>PL0400366</t>
+          <t>PL2542966</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>bartlomiej.zajac70@o2.pl</t>
+          <t>bartlomiej.kaczmarek90@o2.pl</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Irena</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>d.sadowski@yahoocom</t>
+          <t>d.sadowski@yahoo.com</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Sabina</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Mirosława</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Grzegorz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>zuzanna_wrobel.chmielewska@gmail.com</t>
+          <t>zuzanna_wrobel.chmielewska@finanse24.xs</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sławomir</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Henryk</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>m.wilk@finanse24.xs</t>
+          <t>m.wilk@outlook.com</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Ryszard</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Stanisław</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Jacek</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Bartłomiej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Przemysław</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>PL3632241</t>
+          <t>PL2632241</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Damian</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Beata</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Kamil</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Urszula</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>PB2642954</t>
+          <t>PB3642954</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Alicja</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Leszek</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Cezary</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Weronika</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Norbert</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Wiktoria</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Zofia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5733,12 +5733,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Kacper</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Mikołaj</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Szymon</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Kinga</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Antoni</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Aleksander</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Kamila</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Franciszek</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Sylwia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Ignacy</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Halina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nikodem</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Grażyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Danuta</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Miłosz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Bożena</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Aneta</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Tadeusz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Zuzanna</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Jerzy</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Maja</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Marian</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Oliwia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Józef</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t/>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Mirosław</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Gabriela</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>urszula_przybylska@wp.pl</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7386,12 +7386,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Martyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Dominika</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Jagoda</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7689,7 +7689,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>03250748056</t>
+          <t>13250748056</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7776,7 +7776,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14261449404</t>
+          <t>04261449404</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Krystyna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Jadwiga</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Irena</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>olga.panek@wp.pl</t>
+          <t>olga.panek@ubezpiecznia.pl</t>
         </is>
       </c>
     </row>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Sabina</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Mirosława</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Grzegorz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>filiplewandowski@ubezpiecznia.pl</t>
+          <t>filiplewandowski@onet.pl</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Sławomir</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jeryz</t>
+          <t>Jerzy</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Henryk</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Ryszard</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Stanisław</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9909,12 +9909,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Jacek</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Bartłomiej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Przemysław</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Damian</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Beata</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Kamil</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -10344,12 +10344,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Urszula</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Alicja</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Leszek</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Cezary</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Weronika</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Norbert</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Wiktoria</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Zofia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10953,12 +10953,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Kacper</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Mikołaj</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Szymon</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Kinga</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Antoni</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>m.kolodziej@yahoo.com</t>
+          <t>m.kolodziejyahoo.com</t>
         </is>
       </c>
     </row>
@@ -11301,12 +11301,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Aleksander</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Kamila</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Franciszek</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Sylwia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Ignacy</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Halina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Nikodem</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Grażyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>andrzej.wlodarczyk76onet.pl</t>
+          <t>andrzej.wlodarczyk76@onet.pl</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Danuta</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Miłosz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Bożena</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Aneta</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -11910,12 +11910,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Tadeusz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Zuzanna</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -11997,12 +11997,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Jerzy</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Maja</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -12171,12 +12171,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Marian</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Oliwia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -12258,12 +12258,12 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Józef</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>d.wrobel@onet.pl</t>
+          <t>d.wrobel@abxza.pl</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -12519,12 +12519,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Mirosław</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Gabriela</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Martyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Dominika</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Jagoda</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Krystyna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Jadwiga</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>bartlomiej.wysocki94@abxza.pl</t>
+          <t>bartlomiej.wysocki94@o2.pl</t>
         </is>
       </c>
     </row>
@@ -13215,12 +13215,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Irena</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -13476,12 +13476,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Sabina</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Mirosława</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Gajewsik</t>
+          <t>Gajewski</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13824,12 +13824,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -13911,12 +13911,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Grzegorz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -14346,12 +14346,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -14433,12 +14433,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Sławomir</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -14694,12 +14694,12 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -14781,12 +14781,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -14868,12 +14868,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Henryk</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -14955,12 +14955,12 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Ryszard</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Stanisław</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Jacek</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -15216,12 +15216,12 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Bartłomiej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -15303,12 +15303,12 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Przemysław</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -15390,12 +15390,12 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Damian</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Beata</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -15477,12 +15477,12 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Kamil</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Urszula</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -15651,12 +15651,12 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Alicja</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>(48) 778728075</t>
+          <t>(48) 778723123</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -15738,12 +15738,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Leszek</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -15912,12 +15912,12 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Cezary</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Weronika</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -15999,12 +15999,12 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Norbert</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Wiktoria</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -16086,12 +16086,12 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Zofia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Kacper</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Mikołaj</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -16347,12 +16347,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Szymon</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Kinga</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Antoni</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -16521,12 +16521,12 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Aleksander</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Kamila</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>biernat.barbara@interia.pl</t>
+          <t>biernat.barbara@uuu.xs</t>
         </is>
       </c>
     </row>
@@ -16608,12 +16608,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Franciszek</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Sylwia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -16695,12 +16695,12 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Ignacy</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Halina</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -16782,12 +16782,12 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Nikodem</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Grażyna</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -16869,12 +16869,12 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Danuta</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -16956,12 +16956,12 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Miłosz</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Bożena</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -17043,12 +17043,12 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Aneta</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -17130,12 +17130,12 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Tadeusz</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Zuzanna</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -17217,12 +17217,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Jerzy</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Maja</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -17304,12 +17304,12 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Władysław</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Patrycja</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -17391,12 +17391,12 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Marian</t>
+          <t>Waldemar</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Oliwia</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -17478,12 +17478,12 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Józef</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>d.zielinski@uuu.xs</t>
+          <t>d.zielinski@yahoo.com</t>
         </is>
       </c>
     </row>
